--- a/docs/travel/tour-china-2026-10-budget.xlsx
+++ b/docs/travel/tour-china-2026-10-budget.xlsx
@@ -23,11 +23,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="0.##"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="0.##"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -160,12 +159,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -176,27 +175,38 @@
     </xf>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -582,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Giá vé bay, khách sạn là giá tham khảo tra ngày 21/09/2026 qua công cụ tìm kiếm; thay bằng giá Trip.com / Agoda khi tra được. Tiền tệ: CNY, USD hoặc VND.</t>
+          <t>Giá vé bay/khách sạn là GIÁ THẬT tra Trip.com/Google Flights ngày 22/09/2026 qua trình duyệt (vượt tường bot). Sửa ô chữ XANH rồi mở lại bằng Excel/Google Sheets để tự tính. Tiền tệ: CNY, USD hoặc VND.</t>
         </is>
       </c>
     </row>
@@ -592,7 +602,7 @@
           <t>Ngày bắt đầu tour (ngày bay)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="32" t="n">
         <v>46320</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -781,9 +791,9 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="33" t="n">
         <v>350</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -793,7 +803,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Ji Hotel / Orange / Holiday Inn Express 300–400 CNY; Atour Huaqiangbei từ ~72 USD</t>
+          <t>Trip.com 22/09 (Futian, 3-4*): 7Days/RANZ ~280 CNY, Ji/Atour ~570-630; chọn ~350 dễ đạt</t>
         </is>
       </c>
     </row>
@@ -804,9 +814,9 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="33" t="n">
         <v>380</v>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -816,7 +826,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Ji Hotel Hangzhou West Lake từ ~46–63 USD (Kayak, ZenHotels)</t>
+          <t>Trip.com 22/09 (Hubin/Tây Hồ): Zprime 165, Haoyi 236, Mercure 289 CNY → 380 là dư</t>
         </is>
       </c>
     </row>
@@ -829,7 +839,7 @@
       <c r="B17" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="33" t="n">
         <v>400</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -839,7 +849,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Ji Hotel Beijing Wangfujing ~58 USD (Agoda); Atour cao hơn</t>
+          <t>Trip.com 22/09 (Vương Phủ Tỉnh): Zhong an ~298, UrCove Hyatt 574 CNY → 400 đạt, ở ngay VPT vẫn &lt;=1,5tr</t>
         </is>
       </c>
     </row>
@@ -871,7 +881,7 @@
           <t>Ngày kết thúc (ngày bay đêm)</t>
         </is>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="34">
         <f>B3+B18</f>
         <v>46329</v>
       </c>
@@ -909,8 +919,8 @@
           <t>HN đi</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n">
-        <v>142</v>
+      <c r="B23" s="33" t="n">
+        <v>150</v>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
@@ -919,12 +929,12 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>ZH104 HAN 15:05 → SZX 17:50 (Shenzhen Airlines, 23 kg)</t>
+          <t>Shenzhen Airlines HAN 02:10 → SZX 05:00 (bay đêm, hội quân 26/10)</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Expedia HAN–SZX: một chiều từ 144 USD, trung bình 142 USD</t>
+          <t>Trip.com 22/09: rẻ nhất bay thẳng $150; ban ngày China Southern 16:10→19:00 $195</t>
         </is>
       </c>
     </row>
@@ -935,21 +945,21 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>3300000</v>
+        <v>73</v>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>CZ8466 SGN 14:30 → SZX 18:20 (China Southern, 23 kg; tránh Economy Light)</t>
+          <t>Vietravel VU SGN 00:10 → SZX 04:00 (bay đêm rạng sáng 26/10)</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Đại lý CZ VN khứ hồi 5,3–8,5 triệu → một chiều 2,7–4,3 triệu; Skyscanner từ 113 USD</t>
+          <t>Trip.com 22/09: Vietravel $73 (rẻ nhất, hãng mới); CZ8466 ban ngày 14:30→18:15 $209</t>
         </is>
       </c>
     </row>
@@ -959,7 +969,7 @@
           <t>QC đi (tàu)</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B25" s="33" t="n">
         <v>74.5</v>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -984,8 +994,8 @@
           <t>HN về</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n">
-        <v>103</v>
+      <c r="B26" s="33" t="n">
+        <v>152</v>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
@@ -994,12 +1004,12 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>VJ7713 PKX 01:20 → HAN 03:55 (Vietjet)</t>
+          <t>XiamenAir PKX 15:10 → HAN 17:55 (bay thẳng ban NGÀY; đêm 03→04/11 KHÔNG có VietJet thẳng)</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Trip.com / Aviability 8/2026: từ 103 USD</t>
+          <t>Trip.com+Google 22/09: nonstop chỉ Xiamen ban ngày $152; VERIFY app Vietjet lúc book</t>
         </is>
       </c>
     </row>
@@ -1009,8 +1019,8 @@
           <t>SGN + QC về</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
-        <v>103</v>
+      <c r="B27" s="33" t="n">
+        <v>148</v>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
@@ -1019,12 +1029,12 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>VJ3949 PKX 01:05 → SGN 05:00 (Vietjet)</t>
+          <t>VJ3949 PKX 01:05 → SGN 05:00 (Vietjet, SGN + Quảng Châu về chung)</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Cùng mức VJ7713; check web Vietjet</t>
+          <t>Trip.com 22/09: VJ3949 $148 (exclusive fare); đặt thẳng Vietjet.com có thể ~$110</t>
         </is>
       </c>
     </row>
@@ -1059,8 +1069,8 @@
           <t>Bay SZX → HGH</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
-        <v>550</v>
+      <c r="B29" s="33" t="n">
+        <v>597</v>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
@@ -1074,7 +1084,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Skyscanner từ 69 USD, Trip.com từ 74 USD, Kayak từ 81 USD</t>
+          <t>Trip.com 22/09: bay thẳng $90 (~597 CNY), China Southern 07:00→09:00 kèm 20kg</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1094,7 @@
           <t>Tàu Hangzhou East → Beijing South hạng 2</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="33" t="n">
         <v>650</v>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -1136,7 +1146,7 @@
           <t>Ping An Free Sky (vé online)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n">
+      <c r="B33" s="35" t="n">
         <v>180</v>
       </c>
       <c r="C33" s="9" t="n">
@@ -1159,7 +1169,7 @@
           <t>Thuyền Tây Hồ + đảo Tiểu Doanh</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n">
+      <c r="B34" s="35" t="n">
         <v>55</v>
       </c>
       <c r="C34" s="9" t="n">
@@ -1182,7 +1192,7 @@
           <t>Tháp Lôi Phong</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
+      <c r="B35" s="35" t="n">
         <v>40</v>
       </c>
       <c r="C35" s="9" t="n">
@@ -1205,7 +1215,7 @@
           <t>Impression West Lake (vé thường)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
+      <c r="B36" s="35" t="n">
         <v>360</v>
       </c>
       <c r="C36" s="9" t="n">
@@ -1228,7 +1238,7 @@
           <t>Linh Ẩn + Phi Lai Phong (combo)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
+      <c r="B37" s="35" t="n">
         <v>75</v>
       </c>
       <c r="C37" s="9" t="n">
@@ -1251,7 +1261,7 @@
           <t>Mutianyu vé cửa</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
+      <c r="B38" s="35" t="n">
         <v>45</v>
       </c>
       <c r="C38" s="9" t="n">
@@ -1274,7 +1284,7 @@
           <t>Mutianyu shuttle bus</t>
         </is>
       </c>
-      <c r="B39" s="15" t="n">
+      <c r="B39" s="35" t="n">
         <v>15</v>
       </c>
       <c r="C39" s="9" t="n">
@@ -1297,7 +1307,7 @@
           <t>Mutianyu cáp treo / ghế treo + máng trượt (khứ hồi)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
+      <c r="B40" s="35" t="n">
         <v>140</v>
       </c>
       <c r="C40" s="9" t="n">
@@ -1320,7 +1330,7 @@
           <t>Thiên Đàn vé thông (mùa thấp điểm)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
+      <c r="B41" s="35" t="n">
         <v>28</v>
       </c>
       <c r="C41" s="9" t="n">
@@ -1343,7 +1353,7 @@
           <t>Ditan Park (ngân hạnh)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
+      <c r="B42" s="35" t="n">
         <v>10</v>
       </c>
       <c r="C42" s="9" t="n">
@@ -1366,7 +1376,7 @@
           <t>Di Hòa Viên vé thông (mùa thấp điểm)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="n">
+      <c r="B43" s="35" t="n">
         <v>50</v>
       </c>
       <c r="C43" s="9" t="n">
@@ -1389,7 +1399,7 @@
           <t>Hương Sơn (tuỳ chọn)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n">
+      <c r="B44" s="35" t="n">
         <v>15</v>
       </c>
       <c r="C44" s="9" t="n">
@@ -1412,7 +1422,7 @@
           <t>Cảnh Sơn</t>
         </is>
       </c>
-      <c r="B45" s="15" t="n">
+      <c r="B45" s="35" t="n">
         <v>2</v>
       </c>
       <c r="C45" s="9" t="n">
@@ -1435,7 +1445,7 @@
           <t>Tử Cấm Thành (mùa thấp điểm từ 1/11)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
+      <c r="B46" s="35" t="n">
         <v>40</v>
       </c>
       <c r="C46" s="9" t="n">
@@ -1458,7 +1468,7 @@
           <t>Tử Cấm Thành – Trân Bảo Quán</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n">
+      <c r="B47" s="35" t="n">
         <v>10</v>
       </c>
       <c r="C47" s="9" t="n">
@@ -1481,7 +1491,7 @@
           <t>Tử Cấm Thành – Chung Biểu Quán</t>
         </is>
       </c>
-      <c r="B48" s="15" t="n">
+      <c r="B48" s="35" t="n">
         <v>10</v>
       </c>
       <c r="C48" s="9" t="n">
@@ -1504,7 +1514,7 @@
           <t>Ung Hòa Cung (đặt slot giờ)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="n">
+      <c r="B49" s="35" t="n">
         <v>25</v>
       </c>
       <c r="C49" s="9" t="n">
@@ -1527,7 +1537,7 @@
           <t>Tổng vé tham quan / người (CNY)</t>
         </is>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="36">
         <f>SUMPRODUCT(B33:B49,C33:C49)</f>
         <v>1085</v>
       </c>
@@ -1565,7 +1575,7 @@
           <t>Xe 14 chỗ ngày Trường Thành (cả xe, cả ngày)</t>
         </is>
       </c>
-      <c r="B53" s="11" t="n">
+      <c r="B53" s="33" t="n">
         <v>1200</v>
       </c>
       <c r="C53" s="13" t="inlineStr">
@@ -1590,7 +1600,7 @@
           <t>Đi lại nội thành / người / ngày</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n">
+      <c r="B54" s="33" t="n">
         <v>60</v>
       </c>
       <c r="C54" s="13" t="inlineStr">
@@ -1615,7 +1625,7 @@
           <t>Transfer sân bay, ga / người (cả chuyến)</t>
         </is>
       </c>
-      <c r="B55" s="11" t="n">
+      <c r="B55" s="33" t="n">
         <v>150</v>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -1640,7 +1650,7 @@
           <t>Ăn uống / người / ngày</t>
         </is>
       </c>
-      <c r="B56" s="11" t="n">
+      <c r="B56" s="33" t="n">
         <v>180</v>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -1665,7 +1675,7 @@
           <t>eSIM 10 ngày</t>
         </is>
       </c>
-      <c r="B57" s="11" t="n">
+      <c r="B57" s="33" t="n">
         <v>17</v>
       </c>
       <c r="C57" s="13" t="inlineStr">
@@ -1715,7 +1725,7 @@
           <t>Visa: phí lãnh sự</t>
         </is>
       </c>
-      <c r="B59" s="11" t="n">
+      <c r="B59" s="33" t="n">
         <v>60</v>
       </c>
       <c r="C59" s="13" t="inlineStr">
@@ -1832,19 +1842,19 @@
       </c>
       <c r="C4" s="18">
         <f>ChiPhi_HN!$D$23</f>
-        <v>36000120</v>
+        <v>37738990</v>
       </c>
       <c r="D4" s="18">
         <f>ChiPhi_HN!$D$25</f>
-        <v>39600132</v>
+        <v>41512889</v>
       </c>
       <c r="E4" s="18">
         <f>ChiPhi_HN!$E$23</f>
-        <v>72000240</v>
+        <v>75477980</v>
       </c>
       <c r="F4" s="18">
         <f>ChiPhi_HN!$E$25</f>
-        <v>79200264</v>
+        <v>83025778</v>
       </c>
     </row>
     <row r="5">
@@ -1859,19 +1869,19 @@
       </c>
       <c r="C5" s="18">
         <f>ChiPhi_SGN!$D$23</f>
-        <v>35578300</v>
+        <v>35615980</v>
       </c>
       <c r="D5" s="18">
         <f>ChiPhi_SGN!$D$25</f>
-        <v>39136130</v>
+        <v>39177578</v>
       </c>
       <c r="E5" s="18">
         <f>ChiPhi_SGN!$E$23</f>
-        <v>142313200</v>
+        <v>142463920</v>
       </c>
       <c r="F5" s="18">
         <f>ChiPhi_SGN!$E$25</f>
-        <v>156544520</v>
+        <v>156710312</v>
       </c>
     </row>
     <row r="6">
@@ -1886,19 +1896,19 @@
       </c>
       <c r="C6" s="18">
         <f>ChiPhi_QC!$D$23</f>
-        <v>30314975</v>
+        <v>31739325</v>
       </c>
       <c r="D6" s="18">
         <f>ChiPhi_QC!$D$25</f>
-        <v>33346472.5</v>
+        <v>34913257.5</v>
       </c>
       <c r="E6" s="18">
         <f>ChiPhi_QC!$E$23</f>
-        <v>60629950</v>
+        <v>63478650</v>
       </c>
       <c r="F6" s="18">
         <f>ChiPhi_QC!$E$25</f>
-        <v>66692945</v>
+        <v>69826515</v>
       </c>
     </row>
     <row r="7">
@@ -1915,11 +1925,11 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="20">
         <f>SUM(E4:E6)</f>
-        <v>274943390</v>
+        <v/>
       </c>
       <c r="F7" s="20">
         <f>SUM(F4:F6)</f>
-        <v>302437729</v>
+        <v>309562605</v>
       </c>
     </row>
     <row r="9">
@@ -1928,7 +1938,7 @@
           <t>Ngày đi</t>
         </is>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="37">
         <f>ThamSo!$B$3</f>
         <v>46320</v>
       </c>
@@ -1939,7 +1949,7 @@
           <t>Ngày bay về (đêm)</t>
         </is>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="37">
         <f>ThamSo!$B$20</f>
         <v>46329</v>
       </c>
@@ -2008,6 +2018,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>⚠️ Giờ-by-giờ dưới là bản HOẠT ĐỘNG gốc (v3: đáp ban NGÀY, Thâm Quyến 3 / Hàng Châu 2 / Bắc Kinh 4). THỰC TẾ đã đổi: vé bay ĐÊM (SGN Vietravel 00:10→04:00, HN Shenzhen Air 02:10→05:00), HỘI QUÂN sáng 26/10, HN VỀ ban ngày XiamenAir (đêm 03→04/11 không có VietJet thẳng). Sau khi CHỐT option (A=TQ2/HC3/BK4, B=v3, C=TQ3/HC3/BK4) sẽ sắp lại thứ tự ngày cho khớp số đêm. Xem file .md mục 2–4 cho bản cập nhật.</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -2056,7 +2073,7 @@
           <t>Ngày 1</t>
         </is>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="37">
         <f>ThamSo!$B$3+0</f>
         <v>46320</v>
       </c>
@@ -2079,7 +2096,7 @@
           <t>Nhóm SGN có mặt Tân Sơn Nhất T2, nhóm HN có mặt Nội Bài T2</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr"/>
+      <c r="G4" s="36" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Trước giờ bay 2h30</t>
@@ -2092,7 +2109,7 @@
           <t>Ngày 1</t>
         </is>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="37">
         <f>ThamSo!$B$3+0</f>
         <v>46320</v>
       </c>
@@ -2111,7 +2128,7 @@
           <t>Đáp SZX T3 (ZH104 / CZ8466). Nhập cảnh, lấy hành lý, gặp nhau sảnh đến</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr"/>
+      <c r="G5" s="36" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Cùng nhà ga T3</t>
@@ -2124,7 +2141,7 @@
           <t>Ngày 1</t>
         </is>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="37">
         <f>ThamSo!$B$3+0</f>
         <v>46320</v>
       </c>
@@ -2143,7 +2160,7 @@
           <t>Về khách sạn Futian: Metro L11 ~30 phút (~8 CNY) hoặc 2 xe Didi (~100 CNY/xe)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr"/>
+      <c r="G6" s="36" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
@@ -2152,7 +2169,7 @@
           <t>Ngày 1</t>
         </is>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="37">
         <f>ThamSo!$B$3+0</f>
         <v>46320</v>
       </c>
@@ -2171,7 +2188,7 @@
           <t>Nhóm Quảng Châu: tàu G Guangzhou South → Futian (29 phút), về khách sạn</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr"/>
+      <c r="G7" s="36" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Vé 74,5 CNY</t>
@@ -2184,7 +2201,7 @@
           <t>Ngày 1</t>
         </is>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="37">
         <f>ThamSo!$B$3+0</f>
         <v>46320</v>
       </c>
@@ -2203,7 +2220,7 @@
           <t>Cả đoàn ăn tối Coco Park. Kích hoạt eSIM, set Alipay / WeChat Pay</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr"/>
+      <c r="G8" s="36" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
@@ -2212,7 +2229,7 @@
           <t>Ngày 2</t>
         </is>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="37">
         <f>ThamSo!$B$3+1</f>
         <v>46321</v>
       </c>
@@ -2235,7 +2252,7 @@
           <t>[trend] Nantou Ancient Town – cổ thành 1.700 năm cải tạo thành khu cafe, gallery, bar thủ công (Metro L12). Ăn trưa trong khu</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr"/>
+      <c r="G9" s="36" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Miễn phí</t>
@@ -2248,7 +2265,7 @@
           <t>Ngày 2</t>
         </is>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="37">
         <f>ThamSo!$B$3+1</f>
         <v>46321</v>
       </c>
@@ -2267,7 +2284,7 @@
           <t>Huaqiangbei – chợ điện tử lớn nhất TQ: SEG Plaza, Huaqiang Electronic World, Mingtong</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr"/>
+      <c r="G10" s="36" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Miễn phí, mở ~10:00–20:00</t>
@@ -2280,7 +2297,7 @@
           <t>Ngày 2</t>
         </is>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="37">
         <f>ThamSo!$B$3+1</f>
         <v>46321</v>
       </c>
@@ -2299,7 +2316,7 @@
           <t>Ping An Finance Center – Free Sky tầng 116, hoàng hôn ~17:50 (vào cửa cuối 19:15, book bằng hộ chiếu)</t>
         </is>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="38">
         <f>ThamSo!$B$33*ThamSo!$C$33</f>
         <v>180</v>
       </c>
@@ -2315,7 +2332,7 @@
           <t>Ngày 2</t>
         </is>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="37">
         <f>ThamSo!$B$3+1</f>
         <v>46321</v>
       </c>
@@ -2334,7 +2351,7 @@
           <t>Ăn tối Futian</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr"/>
+      <c r="G12" s="36" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
@@ -2343,7 +2360,7 @@
           <t>Ngày 3</t>
         </is>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="37">
         <f>ThamSo!$B$3+2</f>
         <v>46322</v>
       </c>
@@ -2366,7 +2383,7 @@
           <t>Dafen Oil Painting Village – làng tranh sơn dầu, đặt vẽ / mua tranh giá xưởng (Metro L3 ga Dafen, exit A1)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr"/>
+      <c r="G13" s="36" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Miễn phí</t>
@@ -2379,7 +2396,7 @@
           <t>Ngày 3</t>
         </is>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="37">
         <f>ThamSo!$B$3+2</f>
         <v>46322</v>
       </c>
@@ -2398,7 +2415,7 @@
           <t>[trend] Shenzhen MixC World (Nam Sơn) – flagship Huawei, HAUS NOWHERE, cafe; hoặc OCT-LOFT nếu thích nghệ thuật</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr"/>
+      <c r="G14" s="36" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Miễn phí</t>
@@ -2411,7 +2428,7 @@
           <t>Ngày 3</t>
         </is>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="37">
         <f>ThamSo!$B$3+2</f>
         <v>46322</v>
       </c>
@@ -2430,7 +2447,7 @@
           <t>[trend] Shenzhen Talent Park / Shenzhen Bay Park – hoàng hôn, skyline Hong Kong</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr"/>
+      <c r="G15" s="36" t="inlineStr"/>
       <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Miễn phí</t>
@@ -2443,7 +2460,7 @@
           <t>Ngày 3</t>
         </is>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="37">
         <f>ThamSo!$B$3+2</f>
         <v>46322</v>
       </c>
@@ -2462,7 +2479,7 @@
           <t>Ăn tối Sea World (Shekou). Soạn hành lý bay sớm</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr"/>
+      <c r="G16" s="36" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
@@ -2471,7 +2488,7 @@
           <t>Ngày 4</t>
         </is>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="37">
         <f>ThamSo!$B$3+3</f>
         <v>46323</v>
       </c>
@@ -2494,7 +2511,7 @@
           <t>Rời khách sạn ra SZX (30–40 phút)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr"/>
+      <c r="G17" s="36" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
@@ -2503,7 +2520,7 @@
           <t>Ngày 4</t>
         </is>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="37">
         <f>ThamSo!$B$3+3</f>
         <v>46323</v>
       </c>
@@ -2522,7 +2539,7 @@
           <t>Bay SZX → HGH (CZ8711 hoặc chuyến tương đương)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr"/>
+      <c r="G18" s="36" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr">
         <is>
           <t>ThamSo dòng 29</t>
@@ -2535,7 +2552,7 @@
           <t>Ngày 4</t>
         </is>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="37">
         <f>ThamSo!$B$3+3</f>
         <v>46323</v>
       </c>
@@ -2554,7 +2571,7 @@
           <t>HGH → khách sạn khu Hubin (Metro L1/L7 ~1h hoặc taxi ~50 phút). Gửi hành lý</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr"/>
+      <c r="G19" s="36" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
@@ -2563,7 +2580,7 @@
           <t>Ngày 4</t>
         </is>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="37">
         <f>ThamSo!$B$3+3</f>
         <v>46323</v>
       </c>
@@ -2582,7 +2599,7 @@
           <t>Ăn trưa gần Hubin: cá giấm Tây Hồ, thịt Đông Pha</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr"/>
+      <c r="G20" s="36" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
@@ -2591,7 +2608,7 @@
           <t>Ngày 4</t>
         </is>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="37">
         <f>ThamSo!$B$3+3</f>
         <v>46323</v>
       </c>
@@ -2610,7 +2627,7 @@
           <t>Tây Hồ: thuyền ra đảo Tiểu Doanh (chuyến cuối 16:00) → đê Tô → tháp Lôi Phong ngắm hoàng hôn</t>
         </is>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="38">
         <f>ThamSo!$B$34*ThamSo!$C$34</f>
         <v>55</v>
       </c>
@@ -2626,7 +2643,7 @@
           <t>Ngày 4</t>
         </is>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="37">
         <f>ThamSo!$B$3+3</f>
         <v>46323</v>
       </c>
@@ -2641,7 +2658,7 @@
           <t>Tháp Lôi Phong</t>
         </is>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="38">
         <f>ThamSo!$B$35*ThamSo!$C$35</f>
         <v>40</v>
       </c>
@@ -2657,7 +2674,7 @@
           <t>Ngày 4</t>
         </is>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="37">
         <f>ThamSo!$B$3+3</f>
         <v>46323</v>
       </c>
@@ -2676,7 +2693,7 @@
           <t>[trend] Impression West Lake – show Trương Nghệ Mưu trên mặt hồ (82 Beishan Rd). Đặt trước 1–2 tuần</t>
         </is>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="38">
         <f>ThamSo!$B$36*ThamSo!$C$36</f>
         <v>360</v>
       </c>
@@ -2692,7 +2709,7 @@
           <t>Ngày 5</t>
         </is>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="37">
         <f>ThamSo!$B$3+4</f>
         <v>46324</v>
       </c>
@@ -2715,7 +2732,7 @@
           <t>Chùa Linh Ẩn + Phi Lai Phong, đi sớm tránh đông</t>
         </is>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="38">
         <f>ThamSo!$B$37*ThamSo!$C$37</f>
         <v>75</v>
       </c>
@@ -2731,7 +2748,7 @@
           <t>Ngày 5</t>
         </is>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="37">
         <f>ThamSo!$B$3+4</f>
         <v>46324</v>
       </c>
@@ -2750,7 +2767,7 @@
           <t>[trend] Làng trà Long Tỉnh + Mãn Giác Lũng – cafe giữa đồi trà, mùa hoa quế. Ăn trưa nhà dân trồng trà</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr"/>
+      <c r="G25" s="36" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Ăn ~80–120 CNY</t>
@@ -2763,7 +2780,7 @@
           <t>Ngày 5</t>
         </is>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="37">
         <f>ThamSo!$B$3+4</f>
         <v>46324</v>
       </c>
@@ -2782,7 +2799,7 @@
           <t>Bảo tàng Trà quốc gia (nghỉ Thứ Hai)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr"/>
+      <c r="G26" s="36" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
           <t>Miễn phí</t>
@@ -2795,7 +2812,7 @@
           <t>Ngày 5</t>
         </is>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="37">
         <f>ThamSo!$B$3+4</f>
         <v>46324</v>
       </c>
@@ -2814,7 +2831,7 @@
           <t>Cửu Khê (Jiuxi) đi bộ suối giữa rừng trà</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr"/>
+      <c r="G27" s="36" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Miễn phí</t>
@@ -2827,7 +2844,7 @@
           <t>Ngày 5</t>
         </is>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="37">
         <f>ThamSo!$B$3+4</f>
         <v>46324</v>
       </c>
@@ -2846,7 +2863,7 @@
           <t>[trend] Chợ đêm Wulin (17:00–23:00) + đường Wulin; hoặc phố cổ Hà Phường</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr"/>
+      <c r="G28" s="36" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2855,7 +2872,7 @@
           <t>Ngày 6</t>
         </is>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="37">
         <f>ThamSo!$B$3+5</f>
         <v>46325</v>
       </c>
@@ -2878,7 +2895,7 @@
           <t>[trend] Xiaohe Street + cầu Gongchen (Đại Vận Hà) – phố cổ ven kênh, cafe, shop thủ công</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr"/>
+      <c r="G29" s="36" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Miễn phí; trả phòng / gửi hành lý trước</t>
@@ -2891,7 +2908,7 @@
           <t>Ngày 6</t>
         </is>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="37">
         <f>ThamSo!$B$3+5</f>
         <v>46325</v>
       </c>
@@ -2910,7 +2927,7 @@
           <t>Ra ga Hangzhou East (Metro L1/L4 ~30 phút)</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr"/>
+      <c r="G30" s="36" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2919,7 +2936,7 @@
           <t>Ngày 6</t>
         </is>
       </c>
-      <c r="B31" s="21">
+      <c r="B31" s="37">
         <f>ThamSo!$B$3+5</f>
         <v>46325</v>
       </c>
@@ -2938,7 +2955,7 @@
           <t>Tàu G Hangzhou East → Beijing South hạng 2, chọn chuyến ~4,5h</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr"/>
+      <c r="G31" s="36" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr">
         <is>
           <t>ThamSo dòng 30; mở bán 15 ngày trước</t>
@@ -2951,7 +2968,7 @@
           <t>Ngày 6</t>
         </is>
       </c>
-      <c r="B32" s="21">
+      <c r="B32" s="37">
         <f>ThamSo!$B$3+5</f>
         <v>46325</v>
       </c>
@@ -2970,7 +2987,7 @@
           <t>Đến Beijing South → khách sạn Vương Phủ Tỉnh / Đông Đan (2 xe Didi ~40 CNY/xe)</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr"/>
+      <c r="G32" s="36" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2979,7 +2996,7 @@
           <t>Ngày 6</t>
         </is>
       </c>
-      <c r="B33" s="21">
+      <c r="B33" s="37">
         <f>ThamSo!$B$3+5</f>
         <v>46325</v>
       </c>
@@ -2998,7 +3015,7 @@
           <t>Vịt quay Siji Minfu 四季民福 gần Tử Cấm Thành (150–200 CNY/người), đặt bàn hoặc tới sớm</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr"/>
+      <c r="G33" s="36" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Tính trong ăn uống</t>
@@ -3011,7 +3028,7 @@
           <t>Ngày 7</t>
         </is>
       </c>
-      <c r="B34" s="21">
+      <c r="B34" s="37">
         <f>ThamSo!$B$3+6</f>
         <v>46326</v>
       </c>
@@ -3034,7 +3051,7 @@
           <t>Xe riêng 14 chỗ đi Mutianyu (~1h30), đi sớm vì Thứ Bảy đông</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr"/>
+      <c r="G34" s="36" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr">
         <is>
           <t>ThamSo dòng xe</t>
@@ -3047,7 +3064,7 @@
           <t>Ngày 7</t>
         </is>
       </c>
-      <c r="B35" s="21">
+      <c r="B35" s="37">
         <f>ThamSo!$B$3+6</f>
         <v>46326</v>
       </c>
@@ -3066,7 +3083,7 @@
           <t>Vạn Lý Trường Thành Mộ Điền Dục: cáp treo lên tháp 14, đi bộ tới tháp 20, máng trượt xuống (tuỳ thời tiết, không cho 60+)</t>
         </is>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="38">
         <f>ThamSo!$B$38*ThamSo!$C$38</f>
         <v>45</v>
       </c>
@@ -3082,7 +3099,7 @@
           <t>Ngày 7</t>
         </is>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="37">
         <f>ThamSo!$B$3+6</f>
         <v>46326</v>
       </c>
@@ -3097,7 +3114,7 @@
           <t>Shuttle bus bãi xe ↔ cổng</t>
         </is>
       </c>
-      <c r="G36" s="25">
+      <c r="G36" s="38">
         <f>ThamSo!$B$39*ThamSo!$C$39</f>
         <v>15</v>
       </c>
@@ -3109,7 +3126,7 @@
           <t>Ngày 7</t>
         </is>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="37">
         <f>ThamSo!$B$3+6</f>
         <v>46326</v>
       </c>
@@ -3124,7 +3141,7 @@
           <t>Cáp treo / ghế treo + máng trượt khứ hồi</t>
         </is>
       </c>
-      <c r="G37" s="25">
+      <c r="G37" s="38">
         <f>ThamSo!$B$40*ThamSo!$C$40</f>
         <v>140</v>
       </c>
@@ -3140,7 +3157,7 @@
           <t>Ngày 7</t>
         </is>
       </c>
-      <c r="B38" s="21">
+      <c r="B38" s="37">
         <f>ThamSo!$B$3+6</f>
         <v>46326</v>
       </c>
@@ -3159,7 +3176,7 @@
           <t>Ăn trưa chân núi</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr"/>
+      <c r="G38" s="36" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
@@ -3168,7 +3185,7 @@
           <t>Ngày 7</t>
         </is>
       </c>
-      <c r="B39" s="21">
+      <c r="B39" s="37">
         <f>ThamSo!$B$3+6</f>
         <v>46326</v>
       </c>
@@ -3187,7 +3204,7 @@
           <t>[trend] 798 Art Zone – trên đường về từ Mutianyu, gallery mở Thứ Bảy, street art</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr"/>
+      <c r="G39" s="36" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Miễn phí</t>
@@ -3200,7 +3217,7 @@
           <t>Ngày 7</t>
         </is>
       </c>
-      <c r="B40" s="21">
+      <c r="B40" s="37">
         <f>ThamSo!$B$3+6</f>
         <v>46326</v>
       </c>
@@ -3219,7 +3236,7 @@
           <t>Tuỳ chọn: Công viên Olympic – Tổ Chim, Water Cube lên đèn (ngắm ngoài)</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr"/>
+      <c r="G40" s="36" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Miễn phí</t>
@@ -3232,7 +3249,7 @@
           <t>Ngày 7</t>
         </is>
       </c>
-      <c r="B41" s="21">
+      <c r="B41" s="37">
         <f>ThamSo!$B$3+6</f>
         <v>46326</v>
       </c>
@@ -3251,7 +3268,7 @@
           <t>Ăn tối phố Guijie 簋街 (tôm hùm đất, lẩu) hoặc Sanlitun</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr"/>
+      <c r="G41" s="36" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
@@ -3260,7 +3277,7 @@
           <t>Ngày 8</t>
         </is>
       </c>
-      <c r="B42" s="21">
+      <c r="B42" s="37">
         <f>ThamSo!$B$3+7</f>
         <v>46327</v>
       </c>
@@ -3283,7 +3300,7 @@
           <t>Thiên Đàn – sáng sớm dân địa phương tập thái cực</t>
         </is>
       </c>
-      <c r="G42" s="25">
+      <c r="G42" s="38">
         <f>ThamSo!$B$41*ThamSo!$C$41</f>
         <v>28</v>
       </c>
@@ -3295,7 +3312,7 @@
           <t>Ngày 8</t>
         </is>
       </c>
-      <c r="B43" s="21">
+      <c r="B43" s="37">
         <f>ThamSo!$B$3+7</f>
         <v>46327</v>
       </c>
@@ -3314,7 +3331,7 @@
           <t>[trend] Đại lộ ngân hạnh Diaoyutai (đường Sanlihe) – vàng rực cuối 10 đầu 11, đi sớm vì Chủ Nhật; hoặc Ditan Park</t>
         </is>
       </c>
-      <c r="G43" s="25">
+      <c r="G43" s="38">
         <f>ThamSo!$B$42*ThamSo!$C$42</f>
         <v>10</v>
       </c>
@@ -3330,7 +3347,7 @@
           <t>Ngày 8</t>
         </is>
       </c>
-      <c r="B44" s="21">
+      <c r="B44" s="37">
         <f>ThamSo!$B$3+7</f>
         <v>46327</v>
       </c>
@@ -3349,7 +3366,7 @@
           <t>Di Hòa Viên: Trường Lang, thuyền hồ Côn Minh, Phật Hương Các. Ăn trưa gần cổng Đông</t>
         </is>
       </c>
-      <c r="G44" s="25">
+      <c r="G44" s="38">
         <f>ThamSo!$B$43*ThamSo!$C$43</f>
         <v>50</v>
       </c>
@@ -3361,7 +3378,7 @@
           <t>Ngày 8</t>
         </is>
       </c>
-      <c r="B45" s="21">
+      <c r="B45" s="37">
         <f>ThamSo!$B$3+7</f>
         <v>46327</v>
       </c>
@@ -3380,7 +3397,7 @@
           <t>Tuỳ chọn: Hương Sơn mùa lá đỏ (cuối tuần 1–2/11 rất đông; chỉ đi nếu bản tin lá đỏ còn đẹp)</t>
         </is>
       </c>
-      <c r="G45" s="25">
+      <c r="G45" s="38">
         <f>ThamSo!$B$44*ThamSo!$C$44</f>
         <v>0</v>
       </c>
@@ -3396,7 +3413,7 @@
           <t>Ngày 8</t>
         </is>
       </c>
-      <c r="B46" s="21">
+      <c r="B46" s="37">
         <f>ThamSo!$B$3+7</f>
         <v>46327</v>
       </c>
@@ -3415,7 +3432,7 @@
           <t>[trend] Hậu Hải / Thập Sát Hải, Yandai Xiejie, Gulou Dongdajie – ăn tối ven hồ, cafe, bar</t>
         </is>
       </c>
-      <c r="G46" s="16" t="inlineStr"/>
+      <c r="G46" s="36" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Đi Didi 2 xe + metro</t>
@@ -3428,7 +3445,7 @@
           <t>Ngày 9</t>
         </is>
       </c>
-      <c r="B47" s="21">
+      <c r="B47" s="37">
         <f>ThamSo!$B$3+8</f>
         <v>46328</v>
       </c>
@@ -3451,7 +3468,7 @@
           <t>Ung Hòa Cung (Lama Temple) – đặt slot giờ trước bằng hộ chiếu (mở Thứ Hai)</t>
         </is>
       </c>
-      <c r="G47" s="25">
+      <c r="G47" s="38">
         <f>ThamSo!$B$49*ThamSo!$C$49</f>
         <v>25</v>
       </c>
@@ -3463,7 +3480,7 @@
           <t>Ngày 9</t>
         </is>
       </c>
-      <c r="B48" s="21">
+      <c r="B48" s="37">
         <f>ThamSo!$B$3+8</f>
         <v>46328</v>
       </c>
@@ -3482,7 +3499,7 @@
           <t>[trend] Wudaoying hutong – cafe, boutique trong tứ hợp viện (Metal Hands, Fú Dǐng rooftop), Quốc Tử Giám</t>
         </is>
       </c>
-      <c r="G48" s="16" t="inlineStr"/>
+      <c r="G48" s="36" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr">
         <is>
           <t>Miễn phí</t>
@@ -3495,7 +3512,7 @@
           <t>Ngày 9</t>
         </is>
       </c>
-      <c r="B49" s="21">
+      <c r="B49" s="37">
         <f>ThamSo!$B$3+8</f>
         <v>46328</v>
       </c>
@@ -3514,7 +3531,7 @@
           <t>Ăn trưa khu Wudaoying</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr"/>
+      <c r="G49" s="36" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
@@ -3523,7 +3540,7 @@
           <t>Ngày 9</t>
         </is>
       </c>
-      <c r="B50" s="21">
+      <c r="B50" s="37">
         <f>ThamSo!$B$3+8</f>
         <v>46328</v>
       </c>
@@ -3542,7 +3559,7 @@
           <t>[trend] Qianmen + Beijing Fun 北京坊 + Dashilan – phố cổ cải tạo, Page One, Muji Hotel, cafe</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr"/>
+      <c r="G50" s="36" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr">
         <is>
           <t>Miễn phí; Tử Cấm Thành nghỉ Thứ Hai</t>
@@ -3555,7 +3572,7 @@
           <t>Ngày 9</t>
         </is>
       </c>
-      <c r="B51" s="21">
+      <c r="B51" s="37">
         <f>ThamSo!$B$3+8</f>
         <v>46328</v>
       </c>
@@ -3574,7 +3591,7 @@
           <t>Ăn tối Qianmen hoặc Vương Phủ Tỉnh</t>
         </is>
       </c>
-      <c r="G51" s="16" t="inlineStr"/>
+      <c r="G51" s="36" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
@@ -3583,7 +3600,7 @@
           <t>Ngày 10</t>
         </is>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="37">
         <f>ThamSo!$B$3+9</f>
         <v>46329</v>
       </c>
@@ -3606,7 +3623,7 @@
           <t>Quảng trường Thiên An Môn slot sáng (WeChat 天安门广场预约参观, mở 1–9 ngày trước, hộ chiếu gốc)</t>
         </is>
       </c>
-      <c r="G52" s="16" t="inlineStr"/>
+      <c r="G52" s="36" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr">
         <is>
           <t>Miễn phí</t>
@@ -3619,7 +3636,7 @@
           <t>Ngày 10</t>
         </is>
       </c>
-      <c r="B53" s="21">
+      <c r="B53" s="37">
         <f>ThamSo!$B$3+9</f>
         <v>46329</v>
       </c>
@@ -3638,7 +3655,7 @@
           <t>Tử Cấm Thành slot sáng (Thứ Ba, ít đông hơn cuối tuần). Mở bán 20:00 giờ Bắc Kinh 7 ngày trước, 1 vé/hộ chiếu. Ra cổng Bắc</t>
         </is>
       </c>
-      <c r="G53" s="25">
+      <c r="G53" s="38">
         <f>ThamSo!$B$46*ThamSo!$C$46</f>
         <v>40</v>
       </c>
@@ -3654,7 +3671,7 @@
           <t>Ngày 10</t>
         </is>
       </c>
-      <c r="B54" s="21">
+      <c r="B54" s="37">
         <f>ThamSo!$B$3+9</f>
         <v>46329</v>
       </c>
@@ -3669,7 +3686,7 @@
           <t>Trân Bảo Quán (trong Tử Cấm Thành)</t>
         </is>
       </c>
-      <c r="G54" s="25">
+      <c r="G54" s="38">
         <f>ThamSo!$B$47*ThamSo!$C$47</f>
         <v>10</v>
       </c>
@@ -3681,7 +3698,7 @@
           <t>Ngày 10</t>
         </is>
       </c>
-      <c r="B55" s="21">
+      <c r="B55" s="37">
         <f>ThamSo!$B$3+9</f>
         <v>46329</v>
       </c>
@@ -3696,7 +3713,7 @@
           <t>Chung Biểu Quán (trong Tử Cấm Thành)</t>
         </is>
       </c>
-      <c r="G55" s="25">
+      <c r="G55" s="38">
         <f>ThamSo!$B$48*ThamSo!$C$48</f>
         <v>10</v>
       </c>
@@ -3708,7 +3725,7 @@
           <t>Ngày 10</t>
         </is>
       </c>
-      <c r="B56" s="21">
+      <c r="B56" s="37">
         <f>ThamSo!$B$3+9</f>
         <v>46329</v>
       </c>
@@ -3727,7 +3744,7 @@
           <t>Ăn trưa gần Cảnh Sơn</t>
         </is>
       </c>
-      <c r="G56" s="16" t="inlineStr"/>
+      <c r="G56" s="36" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
@@ -3736,7 +3753,7 @@
           <t>Ngày 10</t>
         </is>
       </c>
-      <c r="B57" s="21">
+      <c r="B57" s="37">
         <f>ThamSo!$B$3+9</f>
         <v>46329</v>
       </c>
@@ -3755,7 +3772,7 @@
           <t>Công viên Cảnh Sơn – toàn cảnh Tử Cấm Thành</t>
         </is>
       </c>
-      <c r="G57" s="25">
+      <c r="G57" s="38">
         <f>ThamSo!$B$45*ThamSo!$C$45</f>
         <v>2</v>
       </c>
@@ -3767,7 +3784,7 @@
           <t>Ngày 10</t>
         </is>
       </c>
-      <c r="B58" s="21">
+      <c r="B58" s="37">
         <f>ThamSo!$B$3+9</f>
         <v>46329</v>
       </c>
@@ -3786,7 +3803,7 @@
           <t>Nam La Cổ Hạng + hutong lân cận: xích lô, cafe, ăn vặt</t>
         </is>
       </c>
-      <c r="G58" s="16" t="inlineStr"/>
+      <c r="G58" s="36" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr">
         <is>
           <t>Miễn phí</t>
@@ -3799,7 +3816,7 @@
           <t>Ngày 10</t>
         </is>
       </c>
-      <c r="B59" s="21">
+      <c r="B59" s="37">
         <f>ThamSo!$B$3+9</f>
         <v>46329</v>
       </c>
@@ -3818,7 +3835,7 @@
           <t>Ăn tối gần khách sạn</t>
         </is>
       </c>
-      <c r="G59" s="16" t="inlineStr"/>
+      <c r="G59" s="36" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
@@ -3827,7 +3844,7 @@
           <t>Ngày 10</t>
         </is>
       </c>
-      <c r="B60" s="21">
+      <c r="B60" s="37">
         <f>ThamSo!$B$3+9</f>
         <v>46329</v>
       </c>
@@ -3846,7 +3863,7 @@
           <t>Lấy hành lý, cả 3 nhóm ra Đại Hưng (PKX): Didi ~1h hoặc Metro tới Caoqiao + Daxing Airport Express 35 CNY</t>
         </is>
       </c>
-      <c r="G60" s="16" t="inlineStr"/>
+      <c r="G60" s="36" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
@@ -3855,7 +3872,7 @@
           <t>Ngày 10</t>
         </is>
       </c>
-      <c r="B61" s="21">
+      <c r="B61" s="37">
         <f>ThamSo!$B$3+9</f>
         <v>46329</v>
       </c>
@@ -3874,7 +3891,7 @@
           <t>Hôm sau: VJ3949 về SGN (nhóm SGN + Quảng Châu), VJ7713 về HAN</t>
         </is>
       </c>
-      <c r="G61" s="16" t="inlineStr"/>
+      <c r="G61" s="36" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr">
         <is>
           <t>ThamSo dòng vé về</t>
@@ -3887,7 +3904,7 @@
           <t>Tổng vé (CNY) trong lịch</t>
         </is>
       </c>
-      <c r="G63" s="26">
+      <c r="G63" s="39">
         <f>SUM(G4:G61)</f>
         <v>1085</v>
       </c>
@@ -3958,11 +3975,11 @@
           <t>Visa TQ loại L (nhóm cần visa)</t>
         </is>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="37">
         <f>ThamSo!$B$3</f>
         <v>46320</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="40">
         <f>ThamSo!$B$3-15</f>
         <v>46305</v>
       </c>
@@ -3983,13 +4000,13 @@
           <t>Vé quốc tế đi + về, khách sạn</t>
         </is>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="37">
         <f>ThamSo!$B$3</f>
         <v>46320</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="40">
         <f>TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -4008,11 +4025,11 @@
           <t>Vé tàu Guangzhou South → Futian</t>
         </is>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="37">
         <f>ThamSo!$B$3+0</f>
         <v>46320</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="40">
         <f>ThamSo!$B$3+0-14</f>
         <v>46306</v>
       </c>
@@ -4033,11 +4050,11 @@
           <t>Ping An Free Sky</t>
         </is>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="37">
         <f>ThamSo!$B$3+1</f>
         <v>46321</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="40">
         <f>ThamSo!$B$3+1-1</f>
         <v>46320</v>
       </c>
@@ -4054,11 +4071,11 @@
           <t>Impression West Lake</t>
         </is>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="37">
         <f>ThamSo!$B$3+3</f>
         <v>46323</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="40">
         <f>ThamSo!$B$3+3-14</f>
         <v>46309</v>
       </c>
@@ -4079,11 +4096,11 @@
           <t>Tàu Hangzhou East → Beijing South</t>
         </is>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="37">
         <f>ThamSo!$B$3+5</f>
         <v>46325</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="40">
         <f>ThamSo!$B$3+5-14</f>
         <v>46311</v>
       </c>
@@ -4104,11 +4121,11 @@
           <t>Thiên An Môn (mở đặt từ)</t>
         </is>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="37">
         <f>ThamSo!$B$3+9</f>
         <v>46329</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="40">
         <f>ThamSo!$B$3+9-9</f>
         <v>46320</v>
       </c>
@@ -4129,11 +4146,11 @@
           <t>Tử Cấm Thành (mở bán 20:00 giờ Bắc Kinh)</t>
         </is>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="37">
         <f>ThamSo!$B$3+9</f>
         <v>46329</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="40">
         <f>ThamSo!$B$3+9-7</f>
         <v>46322</v>
       </c>
@@ -4154,11 +4171,11 @@
           <t>Mutianyu + xe 14 chỗ</t>
         </is>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="37">
         <f>ThamSo!$B$3+6</f>
         <v>46326</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="40">
         <f>ThamSo!$B$3+6-7</f>
         <v>46319</v>
       </c>
@@ -4179,11 +4196,11 @@
           <t>Ung Hòa Cung (slot giờ)</t>
         </is>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="37">
         <f>ThamSo!$B$3+8</f>
         <v>46328</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="40">
         <f>ThamSo!$B$3+8-3</f>
         <v>46325</v>
       </c>
@@ -4294,7 +4311,7 @@
           <t>Visa Trung Quốc loại L</t>
         </is>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="41">
         <f>$B$4</f>
         <v>1</v>
       </c>
@@ -4322,20 +4339,20 @@
           <t>Vé đi (tới Thâm Quyến)</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="29">
         <f>IF(ThamSo!$C$23="CNY",ThamSo!$B$23*ThamSo!$B$4,IF(ThamSo!$C$23="USD",ThamSo!$B$23*ThamSo!$B$5,ThamSo!$B$23))</f>
-        <v>3721820</v>
+        <v>3931500</v>
       </c>
       <c r="D8" s="29">
         <f>B8*C8</f>
-        <v>3721820</v>
+        <v>3931500</v>
       </c>
       <c r="E8" s="29">
         <f>D8*$B$2</f>
-        <v>7443640</v>
+        <v>7863000</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -4349,20 +4366,20 @@
           <t>Vé về (Vietjet từ Đại Hưng)</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="29">
         <f>IF(ThamSo!$C$26="CNY",ThamSo!$B$26*ThamSo!$B$4,IF(ThamSo!$C$26="USD",ThamSo!$B$26*ThamSo!$B$5,ThamSo!$B$26))</f>
-        <v>2699630</v>
+        <v>3983920</v>
       </c>
       <c r="D9" s="29">
         <f>B9*C9</f>
-        <v>2699630</v>
+        <v>3983920</v>
       </c>
       <c r="E9" s="29">
         <f>D9*$B$2</f>
-        <v>5399260</v>
+        <v>7967840</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -4376,7 +4393,7 @@
           <t>Hành lý ký gửi Vietjet 20 kg</t>
         </is>
       </c>
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="29">
@@ -4403,20 +4420,20 @@
           <t>Bay SZX → HGH</t>
         </is>
       </c>
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="29">
         <f>IF(ThamSo!$C$29="CNY",ThamSo!$B$29*ThamSo!$B$4,IF(ThamSo!$C$29="USD",ThamSo!$B$29*ThamSo!$B$5,ThamSo!$B$29))</f>
-        <v>2172500</v>
+        <v>2358150</v>
       </c>
       <c r="D11" s="29">
         <f>B11*C11</f>
-        <v>2172500</v>
+        <v>2358150</v>
       </c>
       <c r="E11" s="29">
         <f>D11*$B$2</f>
-        <v>4345000</v>
+        <v>4716300</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -4430,7 +4447,7 @@
           <t>Tàu Hangzhou East → Beijing South</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="29">
@@ -4457,9 +4474,9 @@
           <t>Khách sạn Thâm Quyến</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="41">
         <f>ThamSo!$B$15</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="29">
         <f>ThamSo!$C$15*ThamSo!$B$4*$B$3/$B$2</f>
@@ -4467,11 +4484,11 @@
       </c>
       <c r="D13" s="29">
         <f>B13*C13</f>
-        <v>2073750</v>
+        <v>1382500</v>
       </c>
       <c r="E13" s="29">
         <f>D13*$B$2</f>
-        <v>4147500</v>
+        <v>2765000</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -4485,9 +4502,9 @@
           <t>Khách sạn Hàng Châu</t>
         </is>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="41">
         <f>ThamSo!$B$16</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="29">
         <f>ThamSo!$C$16*ThamSo!$B$4*$B$3/$B$2</f>
@@ -4495,11 +4512,11 @@
       </c>
       <c r="D14" s="29">
         <f>B14*C14</f>
-        <v>1501000</v>
+        <v>2251500</v>
       </c>
       <c r="E14" s="29">
         <f>D14*$B$2</f>
-        <v>3002000</v>
+        <v>4503000</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -4513,7 +4530,7 @@
           <t>Khách sạn Bắc Kinh</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="41">
         <f>ThamSo!$B$17</f>
         <v>4</v>
       </c>
@@ -4541,7 +4558,7 @@
           <t>Vé tham quan (theo bảng ThamSo)</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="29">
@@ -4568,7 +4585,7 @@
           <t>Xe 14 chỗ ngày Trường Thành (chia đều)</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="29">
@@ -4595,7 +4612,7 @@
           <t>Đi lại nội thành</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="41">
         <f>ThamSo!$B$19</f>
         <v>10</v>
       </c>
@@ -4623,7 +4640,7 @@
           <t>Transfer sân bay, ga</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="29">
@@ -4650,7 +4667,7 @@
           <t>Ăn uống</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="41">
         <f>ThamSo!$B$19</f>
         <v>10</v>
       </c>
@@ -4678,7 +4695,7 @@
           <t>eSIM</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="29">
@@ -4705,7 +4722,7 @@
           <t>Bảo hiểm du lịch</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="29">
@@ -4736,11 +4753,11 @@
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="31">
         <f>SUM(D7:D22)</f>
-        <v>36000120</v>
+        <v/>
       </c>
       <c r="E23" s="31">
         <f>SUM(E7:E22)</f>
-        <v>72000240</v>
+        <v>75477980</v>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
@@ -4756,11 +4773,11 @@
       </c>
       <c r="D24" s="29">
         <f>D23*ThamSo!$B$6</f>
-        <v>3600012</v>
+        <v>3773899</v>
       </c>
       <c r="E24" s="29">
         <f>E23*ThamSo!$B$6</f>
-        <v>7200024</v>
+        <v>7547798</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
@@ -4776,11 +4793,11 @@
       </c>
       <c r="D25" s="20">
         <f>D23+D24</f>
-        <v>39600132</v>
+        <v>41512889</v>
       </c>
       <c r="E25" s="20">
         <f>E23+E24</f>
-        <v>79200264</v>
+        <v>83025778</v>
       </c>
     </row>
   </sheetData>
@@ -4883,7 +4900,7 @@
           <t>Visa Trung Quốc loại L</t>
         </is>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="41">
         <f>$B$4</f>
         <v>1</v>
       </c>
@@ -4911,20 +4928,20 @@
           <t>Vé đi (tới Thâm Quyến)</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="29">
         <f>IF(ThamSo!$C$24="CNY",ThamSo!$B$24*ThamSo!$B$4,IF(ThamSo!$C$24="USD",ThamSo!$B$24*ThamSo!$B$5,ThamSo!$B$24))</f>
-        <v>3300000</v>
+        <v>1913330</v>
       </c>
       <c r="D8" s="29">
         <f>B8*C8</f>
-        <v>3300000</v>
+        <v>1913330</v>
       </c>
       <c r="E8" s="29">
         <f>D8*$B$2</f>
-        <v>13200000</v>
+        <v>7653320</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -4938,20 +4955,20 @@
           <t>Vé về (Vietjet từ Đại Hưng)</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="29">
         <f>IF(ThamSo!$C$27="CNY",ThamSo!$B$27*ThamSo!$B$4,IF(ThamSo!$C$27="USD",ThamSo!$B$27*ThamSo!$B$5,ThamSo!$B$27))</f>
-        <v>2699630</v>
+        <v>3879080</v>
       </c>
       <c r="D9" s="29">
         <f>B9*C9</f>
-        <v>2699630</v>
+        <v>3879080</v>
       </c>
       <c r="E9" s="29">
         <f>D9*$B$2</f>
-        <v>10798520</v>
+        <v>15516320</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -4965,7 +4982,7 @@
           <t>Hành lý ký gửi Vietjet 20 kg</t>
         </is>
       </c>
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="29">
@@ -4992,20 +5009,20 @@
           <t>Bay SZX → HGH</t>
         </is>
       </c>
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="29">
         <f>IF(ThamSo!$C$29="CNY",ThamSo!$B$29*ThamSo!$B$4,IF(ThamSo!$C$29="USD",ThamSo!$B$29*ThamSo!$B$5,ThamSo!$B$29))</f>
-        <v>2172500</v>
+        <v>2358150</v>
       </c>
       <c r="D11" s="29">
         <f>B11*C11</f>
-        <v>2172500</v>
+        <v>2358150</v>
       </c>
       <c r="E11" s="29">
         <f>D11*$B$2</f>
-        <v>8690000</v>
+        <v>9432600</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -5019,7 +5036,7 @@
           <t>Tàu Hangzhou East → Beijing South</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="29">
@@ -5046,9 +5063,9 @@
           <t>Khách sạn Thâm Quyến</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="41">
         <f>ThamSo!$B$15</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="29">
         <f>ThamSo!$C$15*ThamSo!$B$4*$B$3/$B$2</f>
@@ -5056,11 +5073,11 @@
       </c>
       <c r="D13" s="29">
         <f>B13*C13</f>
-        <v>2073750</v>
+        <v>1382500</v>
       </c>
       <c r="E13" s="29">
         <f>D13*$B$2</f>
-        <v>8295000</v>
+        <v>5530000</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -5074,9 +5091,9 @@
           <t>Khách sạn Hàng Châu</t>
         </is>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="41">
         <f>ThamSo!$B$16</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="29">
         <f>ThamSo!$C$16*ThamSo!$B$4*$B$3/$B$2</f>
@@ -5084,11 +5101,11 @@
       </c>
       <c r="D14" s="29">
         <f>B14*C14</f>
-        <v>1501000</v>
+        <v>2251500</v>
       </c>
       <c r="E14" s="29">
         <f>D14*$B$2</f>
-        <v>6004000</v>
+        <v>9006000</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -5102,7 +5119,7 @@
           <t>Khách sạn Bắc Kinh</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="41">
         <f>ThamSo!$B$17</f>
         <v>4</v>
       </c>
@@ -5130,7 +5147,7 @@
           <t>Vé tham quan (theo bảng ThamSo)</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="29">
@@ -5157,7 +5174,7 @@
           <t>Xe 14 chỗ ngày Trường Thành (chia đều)</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="29">
@@ -5184,7 +5201,7 @@
           <t>Đi lại nội thành</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="41">
         <f>ThamSo!$B$19</f>
         <v>10</v>
       </c>
@@ -5212,7 +5229,7 @@
           <t>Transfer sân bay, ga</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="29">
@@ -5239,7 +5256,7 @@
           <t>Ăn uống</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="41">
         <f>ThamSo!$B$19</f>
         <v>10</v>
       </c>
@@ -5267,7 +5284,7 @@
           <t>eSIM</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="29">
@@ -5294,7 +5311,7 @@
           <t>Bảo hiểm du lịch</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="29">
@@ -5325,11 +5342,11 @@
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="31">
         <f>SUM(D7:D22)</f>
-        <v>35578300</v>
+        <v/>
       </c>
       <c r="E23" s="31">
         <f>SUM(E7:E22)</f>
-        <v>142313200</v>
+        <v>142463920</v>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
@@ -5345,11 +5362,11 @@
       </c>
       <c r="D24" s="29">
         <f>D23*ThamSo!$B$6</f>
-        <v>3557830</v>
+        <v>3561598</v>
       </c>
       <c r="E24" s="29">
         <f>E23*ThamSo!$B$6</f>
-        <v>14231320</v>
+        <v>14246392</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
@@ -5365,11 +5382,11 @@
       </c>
       <c r="D25" s="20">
         <f>D23+D24</f>
-        <v>39136130</v>
+        <v>39177578</v>
       </c>
       <c r="E25" s="20">
         <f>E23+E24</f>
-        <v>156544520</v>
+        <v>156710312</v>
       </c>
     </row>
   </sheetData>
@@ -5472,7 +5489,7 @@
           <t>Visa Trung Quốc loại L</t>
         </is>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="41">
         <f>$B$4</f>
         <v>0</v>
       </c>
@@ -5500,7 +5517,7 @@
           <t>Vé đi (tới Thâm Quyến)</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="29">
@@ -5527,20 +5544,20 @@
           <t>Vé về (Vietjet từ Đại Hưng)</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="29">
         <f>IF(ThamSo!$C$27="CNY",ThamSo!$B$27*ThamSo!$B$4,IF(ThamSo!$C$27="USD",ThamSo!$B$27*ThamSo!$B$5,ThamSo!$B$27))</f>
-        <v>2699630</v>
+        <v>3879080</v>
       </c>
       <c r="D9" s="29">
         <f>B9*C9</f>
-        <v>2699630</v>
+        <v>3879080</v>
       </c>
       <c r="E9" s="29">
         <f>D9*$B$2</f>
-        <v>5399260</v>
+        <v>7758160</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -5554,7 +5571,7 @@
           <t>Hành lý ký gửi Vietjet 20 kg</t>
         </is>
       </c>
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="29">
@@ -5581,20 +5598,20 @@
           <t>Bay SZX → HGH</t>
         </is>
       </c>
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="29">
         <f>IF(ThamSo!$C$29="CNY",ThamSo!$B$29*ThamSo!$B$4,IF(ThamSo!$C$29="USD",ThamSo!$B$29*ThamSo!$B$5,ThamSo!$B$29))</f>
-        <v>2172500</v>
+        <v>2358150</v>
       </c>
       <c r="D11" s="29">
         <f>B11*C11</f>
-        <v>2172500</v>
+        <v>2358150</v>
       </c>
       <c r="E11" s="29">
         <f>D11*$B$2</f>
-        <v>4345000</v>
+        <v>4716300</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -5608,7 +5625,7 @@
           <t>Tàu Hangzhou East → Beijing South</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="29">
@@ -5635,9 +5652,9 @@
           <t>Khách sạn Thâm Quyến</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="41">
         <f>ThamSo!$B$15</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="29">
         <f>ThamSo!$C$15*ThamSo!$B$4*$B$3/$B$2</f>
@@ -5645,11 +5662,11 @@
       </c>
       <c r="D13" s="29">
         <f>B13*C13</f>
-        <v>2073750</v>
+        <v>1382500</v>
       </c>
       <c r="E13" s="29">
         <f>D13*$B$2</f>
-        <v>4147500</v>
+        <v>2765000</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -5663,9 +5680,9 @@
           <t>Khách sạn Hàng Châu</t>
         </is>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="41">
         <f>ThamSo!$B$16</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="29">
         <f>ThamSo!$C$16*ThamSo!$B$4*$B$3/$B$2</f>
@@ -5673,11 +5690,11 @@
       </c>
       <c r="D14" s="29">
         <f>B14*C14</f>
-        <v>1501000</v>
+        <v>2251500</v>
       </c>
       <c r="E14" s="29">
         <f>D14*$B$2</f>
-        <v>3002000</v>
+        <v>4503000</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -5691,7 +5708,7 @@
           <t>Khách sạn Bắc Kinh</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="41">
         <f>ThamSo!$B$17</f>
         <v>4</v>
       </c>
@@ -5719,7 +5736,7 @@
           <t>Vé tham quan (theo bảng ThamSo)</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="29">
@@ -5746,7 +5763,7 @@
           <t>Xe 14 chỗ ngày Trường Thành (chia đều)</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="29">
@@ -5773,7 +5790,7 @@
           <t>Đi lại nội thành</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="41">
         <f>ThamSo!$B$19</f>
         <v>10</v>
       </c>
@@ -5801,7 +5818,7 @@
           <t>Transfer sân bay, ga</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="29">
@@ -5828,7 +5845,7 @@
           <t>Ăn uống</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="41">
         <f>ThamSo!$B$19</f>
         <v>10</v>
       </c>
@@ -5856,7 +5873,7 @@
           <t>eSIM</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="29">
@@ -5883,7 +5900,7 @@
           <t>Bảo hiểm du lịch</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="42" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="29">
@@ -5914,11 +5931,11 @@
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="31">
         <f>SUM(D7:D22)</f>
-        <v>30314975</v>
+        <v/>
       </c>
       <c r="E23" s="31">
         <f>SUM(E7:E22)</f>
-        <v>60629950</v>
+        <v>63478650</v>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
@@ -5934,11 +5951,11 @@
       </c>
       <c r="D24" s="29">
         <f>D23*ThamSo!$B$6</f>
-        <v>3031497.5</v>
+        <v>3173932.5</v>
       </c>
       <c r="E24" s="29">
         <f>E23*ThamSo!$B$6</f>
-        <v>6062995</v>
+        <v>6347865</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
@@ -5954,11 +5971,11 @@
       </c>
       <c r="D25" s="20">
         <f>D23+D24</f>
-        <v>33346472.5</v>
+        <v>34913257.5</v>
       </c>
       <c r="E25" s="20">
         <f>E23+E24</f>
-        <v>66692945</v>
+        <v>69826515</v>
       </c>
     </row>
   </sheetData>

--- a/docs/travel/tour-china-2026-10-budget.xlsx
+++ b/docs/travel/tour-china-2026-10-budget.xlsx
@@ -2021,7 +2021,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚠️ Giờ-by-giờ dưới là bản HOẠT ĐỘNG gốc (v3: đáp ban NGÀY, Thâm Quyến 3 / Hàng Châu 2 / Bắc Kinh 4). THỰC TẾ đã đổi: vé bay ĐÊM (SGN Vietravel 00:10→04:00, HN Shenzhen Air 02:10→05:00), HỘI QUÂN sáng 26/10, HN VỀ ban ngày XiamenAir (đêm 03→04/11 không có VietJet thẳng). Sau khi CHỐT option (A=TQ2/HC3/BK4, B=v3, C=TQ3/HC3/BK4) sẽ sắp lại thứ tự ngày cho khớp số đêm. Xem file .md mục 2–4 cho bản cập nhật.</t>
+          <t>Lịch Option A (bay đêm đáp sáng 26/10 · Thâm Quyến 1 ngày · Hàng Châu 3 ngày · Bắc Kinh 4 ngày · về đêm 03/11). Ngày tự dời theo ThamSo!B3. Xem file .md mục 3 cho bản chi tiết chỗ ăn/chơi.</t>
         </is>
       </c>
     </row>
@@ -2083,23 +2083,23 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Thâm Quyến</t>
+          <t>Di chuyển</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>12:00 / 12:30</t>
+          <t>chiều/tối</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Nhóm SGN có mặt Tân Sơn Nhất T2, nhóm HN có mặt Nội Bài T2</t>
-        </is>
-      </c>
-      <c r="G4" s="36" t="inlineStr"/>
+          <t>Quảng Châu: tàu G Guangzhou South → Futian (29 phút), nhận 1 phòng nghỉ</t>
+        </is>
+      </c>
+      <c r="G4" s="36" t="n"/>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Trước giờ bay 2h30</t>
+          <t>Vé 74,5 CNY</t>
         </is>
       </c>
     </row>
@@ -2117,111 +2117,119 @@
         <f>CHOOSE(WEEKDAY(B5),"CN","T2","T3","T4","T5","T6","T7")</f>
         <v>CN</v>
       </c>
-      <c r="D5" s="14" t="inlineStr"/>
+      <c r="D5" s="14" t="n"/>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>17:50 / 18:20</t>
+          <t>00:10 / 02:10</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Đáp SZX T3 (ZH104 / CZ8466). Nhập cảnh, lấy hành lý, gặp nhau sảnh đến</t>
-        </is>
-      </c>
-      <c r="G5" s="36" t="inlineStr"/>
+          <t>SGN Vietravel &amp; HN Shenzhen Air bay đêm (khởi hành rạng sáng 26/10)</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="n"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Cùng nhà ga T3</t>
+          <t>Chuẩn bị eSIM, Alipay/WeChat, Didi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Ngày 1</t>
+          <t>Ngày 2</t>
         </is>
       </c>
       <c r="B6" s="37">
-        <f>ThamSo!$B$3+0</f>
-        <v>46320</v>
+        <f>ThamSo!$B$3+1</f>
+        <v>46321</v>
       </c>
       <c r="C6" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B6),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>CN</v>
-      </c>
-      <c r="D6" s="14" t="inlineStr"/>
+        <v>T2</v>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Thâm Quyến</t>
+        </is>
+      </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>04:00 / 05:00</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Về khách sạn Futian: Metro L11 ~30 phút (~8 CNY) hoặc 2 xe Didi (~100 CNY/xe)</t>
-        </is>
-      </c>
-      <c r="G6" s="36" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
+          <t>SGN / HN đáp SZX T3, nhập cảnh → Metro L11 hoặc Didi về Futian, nhận phòng sớm/gửi đồ, nghỉ</t>
+        </is>
+      </c>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Metro L11 ~8 CNY</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>Ngày 1</t>
+          <t>Ngày 2</t>
         </is>
       </c>
       <c r="B7" s="37">
-        <f>ThamSo!$B$3+0</f>
-        <v>46320</v>
+        <f>ThamSo!$B$3+1</f>
+        <v>46321</v>
       </c>
       <c r="C7" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B7),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>CN</v>
-      </c>
-      <c r="D7" s="14" t="inlineStr"/>
+        <v>T2</v>
+      </c>
+      <c r="D7" s="14" t="n"/>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>19:30–20:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Nhóm Quảng Châu: tàu G Guangzhou South → Futian (29 phút), về khách sạn</t>
-        </is>
-      </c>
-      <c r="G7" s="36" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Vé 74,5 CNY</t>
-        </is>
-      </c>
+          <t>Cả đoàn hội quân, ăn brunch, kích hoạt eSIM / ví</t>
+        </is>
+      </c>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Ngày 1</t>
+          <t>Ngày 2</t>
         </is>
       </c>
       <c r="B8" s="37">
-        <f>ThamSo!$B$3+0</f>
-        <v>46320</v>
+        <f>ThamSo!$B$3+1</f>
+        <v>46321</v>
       </c>
       <c r="C8" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B8),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>CN</v>
-      </c>
-      <c r="D8" s="14" t="inlineStr"/>
+        <v>T2</v>
+      </c>
+      <c r="D8" s="14" t="n"/>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>11:00–13:00</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Cả đoàn ăn tối Coco Park. Kích hoạt eSIM, set Alipay / WeChat Pay</t>
-        </is>
-      </c>
-      <c r="G8" s="36" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
+          <t>[trend] Nantou Ancient Town – cổ thành cải tạo cafe, gallery, bar thủ công (Metro L12). Ăn trưa trong khu</t>
+        </is>
+      </c>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2237,22 +2245,18 @@
         <f>CHOOSE(WEEKDAY(B9),"CN","T2","T3","T4","T5","T6","T7")</f>
         <v>T2</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Thâm Quyến</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="n"/>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>09:30–12:30</t>
+          <t>14:30–16:30</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>[trend] Nantou Ancient Town – cổ thành 1.700 năm cải tạo thành khu cafe, gallery, bar thủ công (Metro L12). Ăn trưa trong khu</t>
-        </is>
-      </c>
-      <c r="G9" s="36" t="inlineStr"/>
+          <t>Huaqiangbei – chợ điện tử lớn nhất TQ: SEG Plaza, Huaqiang Electronic World, Mingtong</t>
+        </is>
+      </c>
+      <c r="G9" s="36" t="n"/>
       <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Miễn phí</t>
@@ -2273,21 +2277,24 @@
         <f>CHOOSE(WEEKDAY(B10),"CN","T2","T3","T4","T5","T6","T7")</f>
         <v>T2</v>
       </c>
-      <c r="D10" s="14" t="inlineStr"/>
+      <c r="D10" s="14" t="n"/>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>14:00–16:30</t>
+          <t>17:00–19:00</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Huaqiangbei – chợ điện tử lớn nhất TQ: SEG Plaza, Huaqiang Electronic World, Mingtong</t>
-        </is>
-      </c>
-      <c r="G10" s="36" t="inlineStr"/>
+          <t>Ping An Finance Center – Free Sky tầng 116, hoàng hôn ~17:50 (book bằng hộ chiếu)</t>
+        </is>
+      </c>
+      <c r="G10" s="36">
+        <f>ThamSo!$B$33*ThamSo!$C$33</f>
+        <v>180</v>
+      </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Miễn phí, mở ~10:00–20:00</t>
+          <t>Online 180, quầy 200</t>
         </is>
       </c>
     </row>
@@ -2305,54 +2312,55 @@
         <f>CHOOSE(WEEKDAY(B11),"CN","T2","T3","T4","T5","T6","T7")</f>
         <v>T2</v>
       </c>
-      <c r="D11" s="14" t="inlineStr"/>
+      <c r="D11" s="14" t="n"/>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>17:00–19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Ping An Finance Center – Free Sky tầng 116, hoàng hôn ~17:50 (vào cửa cuối 19:15, book bằng hộ chiếu)</t>
-        </is>
-      </c>
-      <c r="G11" s="38">
-        <f>ThamSo!$B$33*ThamSo!$C$33</f>
-        <v>180</v>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Online 180, quầy 200</t>
-        </is>
-      </c>
+          <t>Ăn tối Coco Park (Futian) – khu ăn uống, bar sôi động</t>
+        </is>
+      </c>
+      <c r="G11" s="38" t="n"/>
+      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Ngày 2</t>
+          <t>Ngày 3</t>
         </is>
       </c>
       <c r="B12" s="37">
-        <f>ThamSo!$B$3+1</f>
-        <v>46321</v>
+        <f>ThamSo!$B$3+2</f>
+        <v>46322</v>
       </c>
       <c r="C12" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B12),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T2</v>
-      </c>
-      <c r="D12" s="14" t="inlineStr"/>
+        <v>T3</v>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Hàng Châu</t>
+        </is>
+      </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>05:45 / 07:00</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Ăn tối Futian</t>
-        </is>
-      </c>
-      <c r="G12" s="36" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
+          <t>Rời khách sạn ra SZX; 07:00 → 09:00 bay SZX → HGH (China Southern)</t>
+        </is>
+      </c>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>ThamSo dòng 29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2368,27 +2376,19 @@
         <f>CHOOSE(WEEKDAY(B13),"CN","T2","T3","T4","T5","T6","T7")</f>
         <v>T3</v>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Thâm Quyến</t>
-        </is>
-      </c>
+      <c r="D13" s="3" t="n"/>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>09:00–12:00</t>
+          <t>10:00–12:00</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Dafen Oil Painting Village – làng tranh sơn dầu, đặt vẽ / mua tranh giá xưởng (Metro L3 ga Dafen, exit A1)</t>
-        </is>
-      </c>
-      <c r="G13" s="36" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
+          <t>Về khách sạn Hubin (Metro L1/L7 ~1h), gửi đồ. Ăn trưa cá giấm Tây Hồ + thịt Đông Pha</t>
+        </is>
+      </c>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -2404,21 +2404,24 @@
         <f>CHOOSE(WEEKDAY(B14),"CN","T2","T3","T4","T5","T6","T7")</f>
         <v>T3</v>
       </c>
-      <c r="D14" s="14" t="inlineStr"/>
+      <c r="D14" s="14" t="n"/>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>14:00–16:00</t>
+          <t>13:30–17:30</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>[trend] Shenzhen MixC World (Nam Sơn) – flagship Huawei, HAUS NOWHERE, cafe; hoặc OCT-LOFT nếu thích nghệ thuật</t>
-        </is>
-      </c>
-      <c r="G14" s="36" t="inlineStr"/>
+          <t>Tây Hồ: thuyền ra đảo Tiểu Doanh (chuyến cuối 16:00) → đê Tô → tháp Lôi Phong hoàng hôn</t>
+        </is>
+      </c>
+      <c r="G14" s="36">
+        <f>ThamSo!$B$34*ThamSo!$C$34</f>
+        <v>55</v>
+      </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Miễn phí</t>
+          <t>Lôi Phong tính dòng dưới</t>
         </is>
       </c>
     </row>
@@ -2436,21 +2439,24 @@
         <f>CHOOSE(WEEKDAY(B15),"CN","T2","T3","T4","T5","T6","T7")</f>
         <v>T3</v>
       </c>
-      <c r="D15" s="14" t="inlineStr"/>
+      <c r="D15" s="14" t="n"/>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>16:30–18:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>[trend] Shenzhen Talent Park / Shenzhen Bay Park – hoàng hôn, skyline Hong Kong</t>
-        </is>
-      </c>
-      <c r="G15" s="36" t="inlineStr"/>
+          <t>Tháp Lôi Phong</t>
+        </is>
+      </c>
+      <c r="G15" s="36">
+        <f>ThamSo!$B$35*ThamSo!$C$35</f>
+        <v>40</v>
+      </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Miễn phí</t>
+          <t>Mùa 11–3 mở tới 17:30</t>
         </is>
       </c>
     </row>
@@ -2468,19 +2474,26 @@
         <f>CHOOSE(WEEKDAY(B16),"CN","T2","T3","T4","T5","T6","T7")</f>
         <v>T3</v>
       </c>
-      <c r="D16" s="14" t="inlineStr"/>
+      <c r="D16" s="14" t="n"/>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:40–20:35</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Ăn tối Sea World (Shekou). Soạn hành lý bay sớm</t>
-        </is>
-      </c>
-      <c r="G16" s="36" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
+          <t>[trend] Impression West Lake – show Trương Nghệ Mưu trên mặt hồ (82 Beishan Rd), đặt trước 1–2 tuần</t>
+        </is>
+      </c>
+      <c r="G16" s="36">
+        <f>ThamSo!$B$36*ThamSo!$C$36</f>
+        <v>360</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>360 / 430 VIP / 960</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2503,16 +2516,23 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>08:00–10:30</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Rời khách sạn ra SZX (30–40 phút)</t>
-        </is>
-      </c>
-      <c r="G17" s="36" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
+          <t>Chùa Linh Ẩn + Phi Lai Phong, đi sớm tránh đông</t>
+        </is>
+      </c>
+      <c r="G17" s="36">
+        <f>ThamSo!$B$37*ThamSo!$C$37</f>
+        <v>75</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>45 + 30</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -2528,21 +2548,21 @@
         <f>CHOOSE(WEEKDAY(B18),"CN","T2","T3","T4","T5","T6","T7")</f>
         <v>T4</v>
       </c>
-      <c r="D18" s="14" t="inlineStr"/>
+      <c r="D18" s="14" t="n"/>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>08:00 → 09:55</t>
+          <t>11:00–14:00</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Bay SZX → HGH (CZ8711 hoặc chuyến tương đương)</t>
-        </is>
-      </c>
-      <c r="G18" s="36" t="inlineStr"/>
+          <t>[trend] Làng trà Long Tỉnh + Mãn Giác Lũng – cafe đồi trà, thưởng trà, ăn trưa nhà dân trồng trà</t>
+        </is>
+      </c>
+      <c r="G18" s="36" t="n"/>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>ThamSo dòng 29</t>
+          <t>Ăn ~80–120 CNY</t>
         </is>
       </c>
     </row>
@@ -2560,19 +2580,23 @@
         <f>CHOOSE(WEEKDAY(B19),"CN","T2","T3","T4","T5","T6","T7")</f>
         <v>T4</v>
       </c>
-      <c r="D19" s="14" t="inlineStr"/>
+      <c r="D19" s="14" t="n"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>10:30–11:30</t>
+          <t>14:30–18:00</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>HGH → khách sạn khu Hubin (Metro L1/L7 ~1h hoặc taxi ~50 phút). Gửi hành lý</t>
-        </is>
-      </c>
-      <c r="G19" s="36" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
+          <t>Bảo tàng Trà quốc gia (miễn phí) → Cửu Khê (Jiuxi) đi bộ suối rừng trà</t>
+        </is>
+      </c>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
@@ -2588,1331 +2612,1052 @@
         <f>CHOOSE(WEEKDAY(B20),"CN","T2","T3","T4","T5","T6","T7")</f>
         <v>T4</v>
       </c>
-      <c r="D20" s="14" t="inlineStr"/>
+      <c r="D20" s="14" t="n"/>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:30–21:00</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Ăn trưa gần Hubin: cá giấm Tây Hồ, thịt Đông Pha</t>
-        </is>
-      </c>
-      <c r="G20" s="36" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
+          <t>[trend] Chợ đêm Wulin (17:00–23:00) – ăn vặt, mua sắm; hoặc phố cổ Hà Phường</t>
+        </is>
+      </c>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Ngày 4</t>
+          <t>Ngày 5</t>
         </is>
       </c>
       <c r="B21" s="37">
-        <f>ThamSo!$B$3+3</f>
-        <v>46323</v>
+        <f>ThamSo!$B$3+4</f>
+        <v>46324</v>
       </c>
       <c r="C21" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B21),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T4</v>
-      </c>
-      <c r="D21" s="14" t="inlineStr"/>
+        <v>T5</v>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Hàng Châu</t>
+        </is>
+      </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>13:30–17:30</t>
+          <t>09:30–12:30</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Tây Hồ: thuyền ra đảo Tiểu Doanh (chuyến cuối 16:00) → đê Tô → tháp Lôi Phong ngắm hoàng hôn</t>
-        </is>
-      </c>
-      <c r="G21" s="38">
-        <f>ThamSo!$B$34*ThamSo!$C$34</f>
-        <v>55</v>
-      </c>
+          <t>[trend] Xiaohe Street + cầu Gongchen (Đại Vận Hà) – phố cổ ven kênh, cafe, bảo tàng nghề. Ăn trưa ven kênh</t>
+        </is>
+      </c>
+      <c r="G21" s="38" t="n"/>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Lôi Phong tính dòng dưới</t>
+          <t>Miễn phí</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Ngày 4</t>
+          <t>Ngày 5</t>
         </is>
       </c>
       <c r="B22" s="37">
-        <f>ThamSo!$B$3+3</f>
-        <v>46323</v>
+        <f>ThamSo!$B$3+4</f>
+        <v>46324</v>
       </c>
       <c r="C22" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B22),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T4</v>
-      </c>
-      <c r="D22" s="14" t="inlineStr"/>
-      <c r="E22" s="14" t="inlineStr"/>
+        <v>T5</v>
+      </c>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>14:00–17:00</t>
+        </is>
+      </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Tháp Lôi Phong</t>
-        </is>
-      </c>
-      <c r="G22" s="38">
-        <f>ThamSo!$B$35*ThamSo!$C$35</f>
-        <v>40</v>
-      </c>
+          <t>Thuê xe đạp vòng Tây Hồ hoặc phố cổ Hà Phường (河坊街) – cafe, quà, kẹo mạch nha; nghỉ lấy sức</t>
+        </is>
+      </c>
+      <c r="G22" s="38" t="n"/>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Mùa 11–3 mở tới 17:30</t>
+          <t>Miễn phí</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>Ngày 4</t>
+          <t>Ngày 5</t>
         </is>
       </c>
       <c r="B23" s="37">
-        <f>ThamSo!$B$3+3</f>
-        <v>46323</v>
+        <f>ThamSo!$B$3+4</f>
+        <v>46324</v>
       </c>
       <c r="C23" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B23),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T4</v>
-      </c>
-      <c r="D23" s="14" t="inlineStr"/>
+        <v>T5</v>
+      </c>
+      <c r="D23" s="14" t="n"/>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>19:40–20:35</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>[trend] Impression West Lake – show Trương Nghệ Mưu trên mặt hồ (82 Beishan Rd). Đặt trước 1–2 tuần</t>
-        </is>
-      </c>
-      <c r="G23" s="38">
-        <f>ThamSo!$B$36*ThamSo!$C$36</f>
-        <v>360</v>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>360 / 430 VIP / 960</t>
-        </is>
-      </c>
+          <t>Ăn tối hải sản / lẩu khu Hubin; tối cafe ven hồ</t>
+        </is>
+      </c>
+      <c r="G23" s="38" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Ngày 5</t>
+          <t>Ngày 6</t>
         </is>
       </c>
       <c r="B24" s="37">
-        <f>ThamSo!$B$3+4</f>
-        <v>46324</v>
+        <f>ThamSo!$B$3+5</f>
+        <v>46325</v>
       </c>
       <c r="C24" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B24),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T5</v>
+        <v>T6</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Hàng Châu</t>
+          <t>Hàng Châu → Bắc Kinh</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>08:00–10:30</t>
+          <t>sáng</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Chùa Linh Ẩn + Phi Lai Phong, đi sớm tránh đông</t>
-        </is>
-      </c>
-      <c r="G24" s="38">
-        <f>ThamSo!$B$37*ThamSo!$C$37</f>
-        <v>75</v>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>45 + 30</t>
-        </is>
-      </c>
+          <t>Cafe Tây Hồ / mua trà Long Tỉnh, lụa Hàng Châu làm quà. Trả phòng, gửi đồ</t>
+        </is>
+      </c>
+      <c r="G24" s="38" t="n"/>
+      <c r="H24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Ngày 5</t>
+          <t>Ngày 6</t>
         </is>
       </c>
       <c r="B25" s="37">
-        <f>ThamSo!$B$3+4</f>
-        <v>46324</v>
+        <f>ThamSo!$B$3+5</f>
+        <v>46325</v>
       </c>
       <c r="C25" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B25),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T5</v>
-      </c>
-      <c r="D25" s="14" t="inlineStr"/>
+        <v>T6</v>
+      </c>
+      <c r="D25" s="14" t="n"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>11:00–14:00</t>
+          <t>11:30–13:30</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>[trend] Làng trà Long Tỉnh + Mãn Giác Lũng – cafe giữa đồi trà, mùa hoa quế. Ăn trưa nhà dân trồng trà</t>
-        </is>
-      </c>
-      <c r="G25" s="36" t="inlineStr"/>
+          <t>Ra ga Hangzhou East → tàu G Hangzhou East → Beijing South hạng 2, ~4,5h</t>
+        </is>
+      </c>
+      <c r="G25" s="36" t="n"/>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Ăn ~80–120 CNY</t>
+          <t>ThamSo dòng 30; mở bán 15 ngày trước</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Ngày 5</t>
+          <t>Ngày 6</t>
         </is>
       </c>
       <c r="B26" s="37">
-        <f>ThamSo!$B$3+4</f>
-        <v>46324</v>
+        <f>ThamSo!$B$3+5</f>
+        <v>46325</v>
       </c>
       <c r="C26" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B26),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T5</v>
-      </c>
-      <c r="D26" s="14" t="inlineStr"/>
+        <v>T6</v>
+      </c>
+      <c r="D26" s="14" t="n"/>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>14:30–16:00</t>
+          <t>~17:30–19:30</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Bảo tàng Trà quốc gia (nghỉ Thứ Hai)</t>
-        </is>
-      </c>
-      <c r="G26" s="36" t="inlineStr"/>
+          <t>Về khách sạn Vương Phủ Tỉnh (Didi ~40 CNY/xe). Vịt quay Siji Minfu 四季民福 gần Tử Cấm Thành</t>
+        </is>
+      </c>
+      <c r="G26" s="36" t="n"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Miễn phí</t>
+          <t>150–200 CNY/người</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Ngày 5</t>
+          <t>Ngày 7</t>
         </is>
       </c>
       <c r="B27" s="37">
-        <f>ThamSo!$B$3+4</f>
-        <v>46324</v>
+        <f>ThamSo!$B$3+6</f>
+        <v>46326</v>
       </c>
       <c r="C27" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B27),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T5</v>
-      </c>
-      <c r="D27" s="14" t="inlineStr"/>
+        <v>T7</v>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Bắc Kinh</t>
+        </is>
+      </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>16:30–18:00</t>
+          <t>07:00–12:30</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Cửu Khê (Jiuxi) đi bộ suối giữa rừng trà</t>
-        </is>
-      </c>
-      <c r="G27" s="36" t="inlineStr"/>
+          <t>Xe riêng 14 chỗ đi Mutianyu (~1h30). Cáp treo tháp 14 → đi bộ tháp 20 → máng trượt (không cho 60+)</t>
+        </is>
+      </c>
+      <c r="G27" s="36">
+        <f>ThamSo!$B$38*ThamSo!$C$38</f>
+        <v>45</v>
+      </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Miễn phí</t>
+          <t>ThamSo dòng xe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Ngày 5</t>
+          <t>Ngày 7</t>
         </is>
       </c>
       <c r="B28" s="37">
-        <f>ThamSo!$B$3+4</f>
-        <v>46324</v>
+        <f>ThamSo!$B$3+6</f>
+        <v>46326</v>
       </c>
       <c r="C28" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B28),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T5</v>
-      </c>
-      <c r="D28" s="14" t="inlineStr"/>
+        <v>T7</v>
+      </c>
+      <c r="D28" s="14" t="n"/>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>18:30–21:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>[trend] Chợ đêm Wulin (17:00–23:00) + đường Wulin; hoặc phố cổ Hà Phường</t>
-        </is>
-      </c>
-      <c r="G28" s="36" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
+          <t>Shuttle bus bãi xe ↔ cổng</t>
+        </is>
+      </c>
+      <c r="G28" s="36">
+        <f>ThamSo!$B$39*ThamSo!$C$39</f>
+        <v>15</v>
+      </c>
+      <c r="H28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Ngày 6</t>
+          <t>Ngày 7</t>
         </is>
       </c>
       <c r="B29" s="37">
-        <f>ThamSo!$B$3+5</f>
-        <v>46325</v>
+        <f>ThamSo!$B$3+6</f>
+        <v>46326</v>
       </c>
       <c r="C29" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B29),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T6</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Hàng Châu → Bắc Kinh</t>
-        </is>
-      </c>
+        <v>T7</v>
+      </c>
+      <c r="D29" s="3" t="n"/>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>09:00–11:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>[trend] Xiaohe Street + cầu Gongchen (Đại Vận Hà) – phố cổ ven kênh, cafe, shop thủ công</t>
-        </is>
-      </c>
-      <c r="G29" s="36" t="inlineStr"/>
+          <t>Cáp treo / ghế treo + máng trượt khứ hồi</t>
+        </is>
+      </c>
+      <c r="G29" s="36">
+        <f>ThamSo!$B$40*ThamSo!$C$40</f>
+        <v>140</v>
+      </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Miễn phí; trả phòng / gửi hành lý trước</t>
+          <t>Một chiều 100</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Ngày 6</t>
+          <t>Ngày 7</t>
         </is>
       </c>
       <c r="B30" s="37">
-        <f>ThamSo!$B$3+5</f>
-        <v>46325</v>
+        <f>ThamSo!$B$3+6</f>
+        <v>46326</v>
       </c>
       <c r="C30" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B30),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T6</v>
-      </c>
-      <c r="D30" s="14" t="inlineStr"/>
+        <v>T7</v>
+      </c>
+      <c r="D30" s="14" t="n"/>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:30–17:30</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Ra ga Hangzhou East (Metro L1/L4 ~30 phút)</t>
-        </is>
-      </c>
-      <c r="G30" s="36" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
+          <t>[trend] 798 Art Zone – trên đường về, gallery, street art</t>
+        </is>
+      </c>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Ngày 6</t>
+          <t>Ngày 7</t>
         </is>
       </c>
       <c r="B31" s="37">
-        <f>ThamSo!$B$3+5</f>
-        <v>46325</v>
+        <f>ThamSo!$B$3+6</f>
+        <v>46326</v>
       </c>
       <c r="C31" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B31),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T6</v>
-      </c>
-      <c r="D31" s="14" t="inlineStr"/>
+        <v>T7</v>
+      </c>
+      <c r="D31" s="14" t="n"/>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>12:00–13:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Tàu G Hangzhou East → Beijing South hạng 2, chọn chuyến ~4,5h</t>
-        </is>
-      </c>
-      <c r="G31" s="36" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>ThamSo dòng 30; mở bán 15 ngày trước</t>
-        </is>
-      </c>
+          <t>Ăn tối phố Guijie 簋街 (tôm hùm đất, lẩu) hoặc Sanlitun</t>
+        </is>
+      </c>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Ngày 6</t>
+          <t>Ngày 8</t>
         </is>
       </c>
       <c r="B32" s="37">
-        <f>ThamSo!$B$3+5</f>
-        <v>46325</v>
+        <f>ThamSo!$B$3+7</f>
+        <v>46327</v>
       </c>
       <c r="C32" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B32),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T6</v>
-      </c>
-      <c r="D32" s="14" t="inlineStr"/>
+        <v>CN</v>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Bắc Kinh</t>
+        </is>
+      </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>~17:30–18:30</t>
+          <t>07:30–09:30</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Đến Beijing South → khách sạn Vương Phủ Tỉnh / Đông Đan (2 xe Didi ~40 CNY/xe)</t>
-        </is>
-      </c>
-      <c r="G32" s="36" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr"/>
+          <t>Thiên Đàn – sáng sớm dân địa phương tập thái cực</t>
+        </is>
+      </c>
+      <c r="G32" s="36">
+        <f>ThamSo!$B$41*ThamSo!$C$41</f>
+        <v>28</v>
+      </c>
+      <c r="H32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Ngày 6</t>
+          <t>Ngày 8</t>
         </is>
       </c>
       <c r="B33" s="37">
-        <f>ThamSo!$B$3+5</f>
-        <v>46325</v>
+        <f>ThamSo!$B$3+7</f>
+        <v>46327</v>
       </c>
       <c r="C33" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B33),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T6</v>
-      </c>
-      <c r="D33" s="14" t="inlineStr"/>
+        <v>CN</v>
+      </c>
+      <c r="D33" s="14" t="n"/>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>10:00–11:00</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Vịt quay Siji Minfu 四季民福 gần Tử Cấm Thành (150–200 CNY/người), đặt bàn hoặc tới sớm</t>
-        </is>
-      </c>
-      <c r="G33" s="36" t="inlineStr"/>
+          <t>[trend] Đại lộ ngân hạnh Diaoyutai (Sanlihe) – vàng rực cuối 10 đầu 11; hoặc Ditan Park</t>
+        </is>
+      </c>
+      <c r="G33" s="36">
+        <f>ThamSo!$B$42*ThamSo!$C$42</f>
+        <v>10</v>
+      </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Tính trong ăn uống</t>
+          <t>Diaoyutai miễn phí; Ditan 10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Ngày 7</t>
+          <t>Ngày 8</t>
         </is>
       </c>
       <c r="B34" s="37">
-        <f>ThamSo!$B$3+6</f>
-        <v>46326</v>
+        <f>ThamSo!$B$3+7</f>
+        <v>46327</v>
       </c>
       <c r="C34" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B34),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T7</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Bắc Kinh</t>
-        </is>
-      </c>
+        <v>CN</v>
+      </c>
+      <c r="D34" s="3" t="n"/>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:30–15:00</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Xe riêng 14 chỗ đi Mutianyu (~1h30), đi sớm vì Thứ Bảy đông</t>
-        </is>
-      </c>
-      <c r="G34" s="36" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>ThamSo dòng xe</t>
-        </is>
-      </c>
+          <t>Di Hòa Viên: Trường Lang, thuyền hồ Côn Minh, Phật Hương Các. Ăn trưa gần cổng Đông</t>
+        </is>
+      </c>
+      <c r="G34" s="36">
+        <f>ThamSo!$B$43*ThamSo!$C$43</f>
+        <v>50</v>
+      </c>
+      <c r="H34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Ngày 7</t>
+          <t>Ngày 8</t>
         </is>
       </c>
       <c r="B35" s="37">
-        <f>ThamSo!$B$3+6</f>
-        <v>46326</v>
+        <f>ThamSo!$B$3+7</f>
+        <v>46327</v>
       </c>
       <c r="C35" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B35),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T7</v>
-      </c>
-      <c r="D35" s="14" t="inlineStr"/>
+        <v>CN</v>
+      </c>
+      <c r="D35" s="14" t="n"/>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>08:45–12:30</t>
+          <t>15:30–17:00</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Vạn Lý Trường Thành Mộ Điền Dục: cáp treo lên tháp 14, đi bộ tới tháp 20, máng trượt xuống (tuỳ thời tiết, không cho 60+)</t>
+          <t>Tuỳ chọn: Hương Sơn mùa lá đỏ (cuối tuần 1–2/11 rất đông; chỉ đi nếu bản tin lá đỏ còn đẹp)</t>
         </is>
       </c>
       <c r="G35" s="38">
-        <f>ThamSo!$B$38*ThamSo!$C$38</f>
-        <v>45</v>
+        <f>ThamSo!$B$44*ThamSo!$C$44</f>
+        <v>0</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>+ shuttle 15 + cáp/máng 140</t>
+          <t>Bật cột 'Tính' ThamSo nếu đi</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Ngày 7</t>
+          <t>Ngày 8</t>
         </is>
       </c>
       <c r="B36" s="37">
-        <f>ThamSo!$B$3+6</f>
-        <v>46326</v>
+        <f>ThamSo!$B$3+7</f>
+        <v>46327</v>
       </c>
       <c r="C36" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B36),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T7</v>
-      </c>
-      <c r="D36" s="14" t="inlineStr"/>
-      <c r="E36" s="14" t="inlineStr"/>
+        <v>CN</v>
+      </c>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Shuttle bus bãi xe ↔ cổng</t>
-        </is>
-      </c>
-      <c r="G36" s="38">
-        <f>ThamSo!$B$39*ThamSo!$C$39</f>
-        <v>15</v>
-      </c>
-      <c r="H36" s="5" t="inlineStr"/>
+          <t>[trend] Hậu Hải / Thập Sát Hải, Yandai Xiejie, Gulou Dongdajie – ăn tối ven hồ, cafe, bar</t>
+        </is>
+      </c>
+      <c r="G36" s="38" t="n"/>
+      <c r="H36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Ngày 7</t>
+          <t>Ngày 9</t>
         </is>
       </c>
       <c r="B37" s="37">
-        <f>ThamSo!$B$3+6</f>
-        <v>46326</v>
+        <f>ThamSo!$B$3+8</f>
+        <v>46328</v>
       </c>
       <c r="C37" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B37),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T7</v>
-      </c>
-      <c r="D37" s="14" t="inlineStr"/>
-      <c r="E37" s="14" t="inlineStr"/>
+        <v>T2</v>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Bắc Kinh</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>09:00–10:30</t>
+        </is>
+      </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Cáp treo / ghế treo + máng trượt khứ hồi</t>
+          <t>Ung Hòa Cung (Lama Temple) – đặt slot giờ trước bằng hộ chiếu</t>
         </is>
       </c>
       <c r="G37" s="38">
-        <f>ThamSo!$B$40*ThamSo!$C$40</f>
-        <v>140</v>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Một chiều 100</t>
-        </is>
-      </c>
+        <f>ThamSo!$B$49*ThamSo!$C$49</f>
+        <v>25</v>
+      </c>
+      <c r="H37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Ngày 7</t>
+          <t>Ngày 9</t>
         </is>
       </c>
       <c r="B38" s="37">
-        <f>ThamSo!$B$3+6</f>
-        <v>46326</v>
+        <f>ThamSo!$B$3+8</f>
+        <v>46328</v>
       </c>
       <c r="C38" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B38),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T7</v>
-      </c>
-      <c r="D38" s="14" t="inlineStr"/>
+        <v>T2</v>
+      </c>
+      <c r="D38" s="14" t="n"/>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30–12:30</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Ăn trưa chân núi</t>
-        </is>
-      </c>
-      <c r="G38" s="36" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
+          <t>[trend] Wudaoying hutong – cafe, boutique tứ hợp viện (Metal Hands, Fú Dǐng rooftop), Quốc Tử Giám</t>
+        </is>
+      </c>
+      <c r="G38" s="36" t="n"/>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Ngày 7</t>
+          <t>Ngày 9</t>
         </is>
       </c>
       <c r="B39" s="37">
-        <f>ThamSo!$B$3+6</f>
-        <v>46326</v>
+        <f>ThamSo!$B$3+8</f>
+        <v>46328</v>
       </c>
       <c r="C39" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B39),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T7</v>
-      </c>
-      <c r="D39" s="14" t="inlineStr"/>
+        <v>T2</v>
+      </c>
+      <c r="D39" s="14" t="n"/>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>15:30–17:30</t>
+          <t>14:00–17:00</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>[trend] 798 Art Zone – trên đường về từ Mutianyu, gallery mở Thứ Bảy, street art</t>
-        </is>
-      </c>
-      <c r="G39" s="36" t="inlineStr"/>
+          <t>[trend] Qianmen + Beijing Fun 北京坊 + Dashilan – phố cổ cải tạo, Page One, Muji Hotel, cafe</t>
+        </is>
+      </c>
+      <c r="G39" s="36" t="n"/>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Miễn phí</t>
+          <t>Miễn phí; Tử Cấm Thành nghỉ T2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Ngày 7</t>
+          <t>Ngày 9</t>
         </is>
       </c>
       <c r="B40" s="37">
-        <f>ThamSo!$B$3+6</f>
-        <v>46326</v>
+        <f>ThamSo!$B$3+8</f>
+        <v>46328</v>
       </c>
       <c r="C40" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B40),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T7</v>
-      </c>
-      <c r="D40" s="14" t="inlineStr"/>
+        <v>T2</v>
+      </c>
+      <c r="D40" s="14" t="n"/>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>18:00–19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Tuỳ chọn: Công viên Olympic – Tổ Chim, Water Cube lên đèn (ngắm ngoài)</t>
-        </is>
-      </c>
-      <c r="G40" s="36" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
+          <t>Ăn tối Qianmen hoặc Vương Phủ Tỉnh</t>
+        </is>
+      </c>
+      <c r="G40" s="36" t="n"/>
+      <c r="H40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Ngày 7</t>
+          <t>Ngày 10</t>
         </is>
       </c>
       <c r="B41" s="37">
-        <f>ThamSo!$B$3+6</f>
-        <v>46326</v>
+        <f>ThamSo!$B$3+9</f>
+        <v>46329</v>
       </c>
       <c r="C41" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B41),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T7</v>
-      </c>
-      <c r="D41" s="14" t="inlineStr"/>
+        <v>T3</v>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>Bắc Kinh → bay đêm</t>
+        </is>
+      </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Ăn tối phố Guijie 簋街 (tôm hùm đất, lẩu) hoặc Sanlitun</t>
-        </is>
-      </c>
-      <c r="G41" s="36" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
+          <t>Quảng trường Thiên An Môn slot sáng (WeChat 天安门广场预约参观, hộ chiếu gốc)</t>
+        </is>
+      </c>
+      <c r="G41" s="36" t="n"/>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Ngày 8</t>
+          <t>Ngày 10</t>
         </is>
       </c>
       <c r="B42" s="37">
-        <f>ThamSo!$B$3+7</f>
-        <v>46327</v>
+        <f>ThamSo!$B$3+9</f>
+        <v>46329</v>
       </c>
       <c r="C42" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B42),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>CN</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Bắc Kinh</t>
-        </is>
-      </c>
+        <v>T3</v>
+      </c>
+      <c r="D42" s="3" t="n"/>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>07:30–09:30</t>
+          <t>09:00–12:30</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Thiên Đàn – sáng sớm dân địa phương tập thái cực</t>
+          <t>Tử Cấm Thành slot sáng (mở bán 20:00 giờ BK 7 ngày trước, 1 vé/hộ chiếu). Trả phòng trước 12:00</t>
         </is>
       </c>
       <c r="G42" s="38">
-        <f>ThamSo!$B$41*ThamSo!$C$41</f>
-        <v>28</v>
-      </c>
-      <c r="H42" s="5" t="inlineStr"/>
+        <f>ThamSo!$B$46*ThamSo!$C$46</f>
+        <v>40</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Gửi hành lý ở khách sạn</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Ngày 8</t>
+          <t>Ngày 10</t>
         </is>
       </c>
       <c r="B43" s="37">
-        <f>ThamSo!$B$3+7</f>
-        <v>46327</v>
+        <f>ThamSo!$B$3+9</f>
+        <v>46329</v>
       </c>
       <c r="C43" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B43),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>CN</v>
-      </c>
-      <c r="D43" s="14" t="inlineStr"/>
+        <v>T3</v>
+      </c>
+      <c r="D43" s="14" t="n"/>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>10:00–11:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>[trend] Đại lộ ngân hạnh Diaoyutai (đường Sanlihe) – vàng rực cuối 10 đầu 11, đi sớm vì Chủ Nhật; hoặc Ditan Park</t>
+          <t>Trân Bảo Quán (trong Tử Cấm Thành)</t>
         </is>
       </c>
       <c r="G43" s="38">
-        <f>ThamSo!$B$42*ThamSo!$C$42</f>
+        <f>ThamSo!$B$47*ThamSo!$C$47</f>
         <v>10</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Diaoyutai miễn phí; Ditan 10</t>
-        </is>
-      </c>
+      <c r="H43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Ngày 8</t>
+          <t>Ngày 10</t>
         </is>
       </c>
       <c r="B44" s="37">
-        <f>ThamSo!$B$3+7</f>
-        <v>46327</v>
+        <f>ThamSo!$B$3+9</f>
+        <v>46329</v>
       </c>
       <c r="C44" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B44),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>CN</v>
-      </c>
-      <c r="D44" s="14" t="inlineStr"/>
+        <v>T3</v>
+      </c>
+      <c r="D44" s="14" t="n"/>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>11:30–15:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Di Hòa Viên: Trường Lang, thuyền hồ Côn Minh, Phật Hương Các. Ăn trưa gần cổng Đông</t>
+          <t>Chung Biểu Quán (trong Tử Cấm Thành)</t>
         </is>
       </c>
       <c r="G44" s="38">
-        <f>ThamSo!$B$43*ThamSo!$C$43</f>
-        <v>50</v>
-      </c>
-      <c r="H44" s="5" t="inlineStr"/>
+        <f>ThamSo!$B$48*ThamSo!$C$48</f>
+        <v>10</v>
+      </c>
+      <c r="H44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Ngày 8</t>
+          <t>Ngày 10</t>
         </is>
       </c>
       <c r="B45" s="37">
-        <f>ThamSo!$B$3+7</f>
-        <v>46327</v>
+        <f>ThamSo!$B$3+9</f>
+        <v>46329</v>
       </c>
       <c r="C45" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B45),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>CN</v>
-      </c>
-      <c r="D45" s="14" t="inlineStr"/>
+        <v>T3</v>
+      </c>
+      <c r="D45" s="14" t="n"/>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>15:30–17:00</t>
+          <t>14:00–15:30</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Tuỳ chọn: Hương Sơn mùa lá đỏ (cuối tuần 1–2/11 rất đông; chỉ đi nếu bản tin lá đỏ còn đẹp)</t>
+          <t>Công viên Cảnh Sơn – toàn cảnh Tử Cấm Thành (SGN+QC); nhóm HN ~13:00 ra sân bay bay Xiamen 15:10</t>
         </is>
       </c>
       <c r="G45" s="38">
-        <f>ThamSo!$B$44*ThamSo!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>Bật cột 'Tính' ở ThamSo nếu đi</t>
-        </is>
-      </c>
+        <f>ThamSo!$B$45*ThamSo!$C$45</f>
+        <v>2</v>
+      </c>
+      <c r="H45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Ngày 8</t>
+          <t>Ngày 10</t>
         </is>
       </c>
       <c r="B46" s="37">
-        <f>ThamSo!$B$3+7</f>
-        <v>46327</v>
+        <f>ThamSo!$B$3+9</f>
+        <v>46329</v>
       </c>
       <c r="C46" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B46),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>CN</v>
-      </c>
-      <c r="D46" s="14" t="inlineStr"/>
+        <v>T3</v>
+      </c>
+      <c r="D46" s="14" t="n"/>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00–18:00</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>[trend] Hậu Hải / Thập Sát Hải, Yandai Xiejie, Gulou Dongdajie – ăn tối ven hồ, cafe, bar</t>
-        </is>
-      </c>
-      <c r="G46" s="36" t="inlineStr"/>
+          <t>Nam La Cổ Hạng + hutong lân cận: cafe, ăn vặt (SGN+QC)</t>
+        </is>
+      </c>
+      <c r="G46" s="36" t="n"/>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Đi Didi 2 xe + metro</t>
+          <t>Miễn phí</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Ngày 9</t>
+          <t>Ngày 10</t>
         </is>
       </c>
       <c r="B47" s="37">
-        <f>ThamSo!$B$3+8</f>
-        <v>46328</v>
+        <f>ThamSo!$B$3+9</f>
+        <v>46329</v>
       </c>
       <c r="C47" s="14" t="str">
         <f>CHOOSE(WEEKDAY(B47),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T2</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Bắc Kinh</t>
-        </is>
-      </c>
+        <v>T3</v>
+      </c>
+      <c r="D47" s="3" t="n"/>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>09:00–10:30</t>
+          <t>21:00 / 21:30</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Ung Hòa Cung (Lama Temple) – đặt slot giờ trước bằng hộ chiếu (mở Thứ Hai)</t>
-        </is>
-      </c>
-      <c r="G47" s="38">
-        <f>ThamSo!$B$49*ThamSo!$C$49</f>
-        <v>25</v>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
+          <t>SGN+QC lấy hành lý, ra Đại Hưng (PKX): Didi ~1h hoặc Metro + Daxing Express 35 CNY. 01:05 VJ3949</t>
+        </is>
+      </c>
+      <c r="G47" s="38" t="n"/>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>ThamSo dòng vé về</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>Ngày 9</t>
-        </is>
-      </c>
-      <c r="B48" s="37">
-        <f>ThamSo!$B$3+8</f>
-        <v>46328</v>
-      </c>
-      <c r="C48" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B48),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T2</v>
-      </c>
-      <c r="D48" s="14" t="inlineStr"/>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>10:30–12:30</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>[trend] Wudaoying hutong – cafe, boutique trong tứ hợp viện (Metal Hands, Fú Dǐng rooftop), Quốc Tử Giám</t>
-        </is>
-      </c>
-      <c r="G48" s="36" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
+      <c r="A48" s="14" t="n"/>
+      <c r="B48" s="37" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="36" t="n"/>
+      <c r="H48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Ngày 9</t>
-        </is>
-      </c>
-      <c r="B49" s="37">
-        <f>ThamSo!$B$3+8</f>
-        <v>46328</v>
-      </c>
-      <c r="C49" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B49),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T2</v>
-      </c>
-      <c r="D49" s="14" t="inlineStr"/>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Ăn trưa khu Wudaoying</t>
-        </is>
-      </c>
-      <c r="G49" s="36" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
+          <t>Tổng vé (CNY) trong lịch</t>
+        </is>
+      </c>
+      <c r="B49" s="37" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="36">
+        <f>SUM(G4:G47)</f>
+        <v/>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Bằng ThamSo tổng vé (dòng tắt cột 'Tính' = 0 tính bằng 0)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>Ngày 9</t>
-        </is>
-      </c>
-      <c r="B50" s="37">
-        <f>ThamSo!$B$3+8</f>
-        <v>46328</v>
-      </c>
-      <c r="C50" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B50),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T2</v>
-      </c>
-      <c r="D50" s="14" t="inlineStr"/>
-      <c r="E50" s="14" t="inlineStr">
-        <is>
-          <t>14:00–17:00</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>[trend] Qianmen + Beijing Fun 北京坊 + Dashilan – phố cổ cải tạo, Page One, Muji Hotel, cafe</t>
-        </is>
-      </c>
-      <c r="G50" s="36" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>Miễn phí; Tử Cấm Thành nghỉ Thứ Hai</t>
-        </is>
-      </c>
+      <c r="A50" s="14" t="n"/>
+      <c r="B50" s="37" t="n"/>
+      <c r="C50" s="14" t="n"/>
+      <c r="D50" s="14" t="n"/>
+      <c r="E50" s="14" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="36" t="n"/>
+      <c r="H50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t>Ngày 9</t>
-        </is>
-      </c>
-      <c r="B51" s="37">
-        <f>ThamSo!$B$3+8</f>
-        <v>46328</v>
-      </c>
-      <c r="C51" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B51),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T2</v>
-      </c>
-      <c r="D51" s="14" t="inlineStr"/>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Ăn tối Qianmen hoặc Vương Phủ Tỉnh</t>
-        </is>
-      </c>
-      <c r="G51" s="36" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr"/>
+      <c r="A51" s="14" t="n"/>
+      <c r="B51" s="37" t="n"/>
+      <c r="C51" s="14" t="n"/>
+      <c r="D51" s="14" t="n"/>
+      <c r="E51" s="14" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="36" t="n"/>
+      <c r="H51" s="5" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Ngày 10</t>
-        </is>
-      </c>
-      <c r="B52" s="37">
-        <f>ThamSo!$B$3+9</f>
-        <v>46329</v>
-      </c>
-      <c r="C52" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B52),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T3</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Bắc Kinh → bay đêm</t>
-        </is>
-      </c>
-      <c r="E52" s="14" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>Quảng trường Thiên An Môn slot sáng (WeChat 天安门广场预约参观, mở 1–9 ngày trước, hộ chiếu gốc)</t>
-        </is>
-      </c>
-      <c r="G52" s="36" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
+      <c r="A52" s="3" t="n"/>
+      <c r="B52" s="37" t="n"/>
+      <c r="C52" s="14" t="n"/>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="14" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="36" t="n"/>
+      <c r="H52" s="5" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>Ngày 10</t>
-        </is>
-      </c>
-      <c r="B53" s="37">
-        <f>ThamSo!$B$3+9</f>
-        <v>46329</v>
-      </c>
-      <c r="C53" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B53),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T3</v>
-      </c>
-      <c r="D53" s="14" t="inlineStr"/>
-      <c r="E53" s="14" t="inlineStr">
-        <is>
-          <t>09:00–12:30</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>Tử Cấm Thành slot sáng (Thứ Ba, ít đông hơn cuối tuần). Mở bán 20:00 giờ Bắc Kinh 7 ngày trước, 1 vé/hộ chiếu. Ra cổng Bắc</t>
-        </is>
-      </c>
-      <c r="G53" s="38">
-        <f>ThamSo!$B$46*ThamSo!$C$46</f>
-        <v>40</v>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>Trả phòng trước 12:00, gửi hành lý ở khách sạn</t>
-        </is>
-      </c>
+      <c r="A53" s="14" t="n"/>
+      <c r="B53" s="37" t="n"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="14" t="n"/>
+      <c r="E53" s="14" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="38" t="n"/>
+      <c r="H53" s="5" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>Ngày 10</t>
-        </is>
-      </c>
-      <c r="B54" s="37">
-        <f>ThamSo!$B$3+9</f>
-        <v>46329</v>
-      </c>
-      <c r="C54" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B54),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T3</v>
-      </c>
-      <c r="D54" s="14" t="inlineStr"/>
-      <c r="E54" s="14" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>Trân Bảo Quán (trong Tử Cấm Thành)</t>
-        </is>
-      </c>
-      <c r="G54" s="38">
-        <f>ThamSo!$B$47*ThamSo!$C$47</f>
-        <v>10</v>
-      </c>
-      <c r="H54" s="5" t="inlineStr"/>
+      <c r="A54" s="14" t="n"/>
+      <c r="B54" s="37" t="n"/>
+      <c r="C54" s="14" t="n"/>
+      <c r="D54" s="14" t="n"/>
+      <c r="E54" s="14" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="38" t="n"/>
+      <c r="H54" s="5" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="inlineStr">
-        <is>
-          <t>Ngày 10</t>
-        </is>
-      </c>
-      <c r="B55" s="37">
-        <f>ThamSo!$B$3+9</f>
-        <v>46329</v>
-      </c>
-      <c r="C55" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B55),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T3</v>
-      </c>
-      <c r="D55" s="14" t="inlineStr"/>
-      <c r="E55" s="14" t="inlineStr"/>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>Chung Biểu Quán (trong Tử Cấm Thành)</t>
-        </is>
-      </c>
-      <c r="G55" s="38">
-        <f>ThamSo!$B$48*ThamSo!$C$48</f>
-        <v>10</v>
-      </c>
-      <c r="H55" s="5" t="inlineStr"/>
+      <c r="A55" s="14" t="n"/>
+      <c r="B55" s="37" t="n"/>
+      <c r="C55" s="14" t="n"/>
+      <c r="D55" s="14" t="n"/>
+      <c r="E55" s="14" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="38" t="n"/>
+      <c r="H55" s="5" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="14" t="inlineStr">
-        <is>
-          <t>Ngày 10</t>
-        </is>
-      </c>
-      <c r="B56" s="37">
-        <f>ThamSo!$B$3+9</f>
-        <v>46329</v>
-      </c>
-      <c r="C56" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B56),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T3</v>
-      </c>
-      <c r="D56" s="14" t="inlineStr"/>
-      <c r="E56" s="14" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>Ăn trưa gần Cảnh Sơn</t>
-        </is>
-      </c>
-      <c r="G56" s="36" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr"/>
+      <c r="A56" s="14" t="n"/>
+      <c r="B56" s="37" t="n"/>
+      <c r="C56" s="14" t="n"/>
+      <c r="D56" s="14" t="n"/>
+      <c r="E56" s="14" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="36" t="n"/>
+      <c r="H56" s="5" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>Ngày 10</t>
-        </is>
-      </c>
-      <c r="B57" s="37">
-        <f>ThamSo!$B$3+9</f>
-        <v>46329</v>
-      </c>
-      <c r="C57" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B57),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T3</v>
-      </c>
-      <c r="D57" s="14" t="inlineStr"/>
-      <c r="E57" s="14" t="inlineStr">
-        <is>
-          <t>14:00–15:30</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>Công viên Cảnh Sơn – toàn cảnh Tử Cấm Thành</t>
-        </is>
-      </c>
-      <c r="G57" s="38">
-        <f>ThamSo!$B$45*ThamSo!$C$45</f>
-        <v>2</v>
-      </c>
-      <c r="H57" s="5" t="inlineStr"/>
+      <c r="A57" s="14" t="n"/>
+      <c r="B57" s="37" t="n"/>
+      <c r="C57" s="14" t="n"/>
+      <c r="D57" s="14" t="n"/>
+      <c r="E57" s="14" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="38" t="n"/>
+      <c r="H57" s="5" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>Ngày 10</t>
-        </is>
-      </c>
-      <c r="B58" s="37">
-        <f>ThamSo!$B$3+9</f>
-        <v>46329</v>
-      </c>
-      <c r="C58" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B58),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T3</v>
-      </c>
-      <c r="D58" s="14" t="inlineStr"/>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>16:00–18:00</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>Nam La Cổ Hạng + hutong lân cận: xích lô, cafe, ăn vặt</t>
-        </is>
-      </c>
-      <c r="G58" s="36" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
+      <c r="A58" s="14" t="n"/>
+      <c r="B58" s="37" t="n"/>
+      <c r="C58" s="14" t="n"/>
+      <c r="D58" s="14" t="n"/>
+      <c r="E58" s="14" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="36" t="n"/>
+      <c r="H58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>Ngày 10</t>
-        </is>
-      </c>
-      <c r="B59" s="37">
-        <f>ThamSo!$B$3+9</f>
-        <v>46329</v>
-      </c>
-      <c r="C59" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B59),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T3</v>
-      </c>
-      <c r="D59" s="14" t="inlineStr"/>
-      <c r="E59" s="14" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>Ăn tối gần khách sạn</t>
-        </is>
-      </c>
-      <c r="G59" s="36" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr"/>
+      <c r="A59" s="14" t="n"/>
+      <c r="B59" s="37" t="n"/>
+      <c r="C59" s="14" t="n"/>
+      <c r="D59" s="14" t="n"/>
+      <c r="E59" s="14" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="36" t="n"/>
+      <c r="H59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>Ngày 10</t>
-        </is>
-      </c>
-      <c r="B60" s="37">
-        <f>ThamSo!$B$3+9</f>
-        <v>46329</v>
-      </c>
-      <c r="C60" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B60),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T3</v>
-      </c>
-      <c r="D60" s="14" t="inlineStr"/>
-      <c r="E60" s="14" t="inlineStr">
-        <is>
-          <t>21:00 / 21:30</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>Lấy hành lý, cả 3 nhóm ra Đại Hưng (PKX): Didi ~1h hoặc Metro tới Caoqiao + Daxing Airport Express 35 CNY</t>
-        </is>
-      </c>
-      <c r="G60" s="36" t="inlineStr"/>
-      <c r="H60" s="5" t="inlineStr"/>
+      <c r="A60" s="14" t="n"/>
+      <c r="B60" s="37" t="n"/>
+      <c r="C60" s="14" t="n"/>
+      <c r="D60" s="14" t="n"/>
+      <c r="E60" s="14" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="36" t="n"/>
+      <c r="H60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="14" t="inlineStr">
-        <is>
-          <t>Ngày 10</t>
-        </is>
-      </c>
-      <c r="B61" s="37">
-        <f>ThamSo!$B$3+9</f>
-        <v>46329</v>
-      </c>
-      <c r="C61" s="14" t="str">
-        <f>CHOOSE(WEEKDAY(B61),"CN","T2","T3","T4","T5","T6","T7")</f>
-        <v>T3</v>
-      </c>
-      <c r="D61" s="14" t="inlineStr"/>
-      <c r="E61" s="14" t="inlineStr">
-        <is>
-          <t>01:05 / 01:20</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>Hôm sau: VJ3949 về SGN (nhóm SGN + Quảng Châu), VJ7713 về HAN</t>
-        </is>
-      </c>
-      <c r="G61" s="36" t="inlineStr"/>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>ThamSo dòng vé về</t>
-        </is>
-      </c>
-    </row>
+      <c r="A61" s="14" t="n"/>
+      <c r="B61" s="37" t="n"/>
+      <c r="C61" s="14" t="n"/>
+      <c r="D61" s="14" t="n"/>
+      <c r="E61" s="14" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="36" t="n"/>
+      <c r="H61" s="5" t="n"/>
+    </row>
+    <row r="62"/>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>Tổng vé (CNY) trong lịch</t>
-        </is>
-      </c>
-      <c r="G63" s="39">
-        <f>SUM(G4:G61)</f>
-        <v>1085</v>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>Bằng ThamSo tổng vé (dòng tắt cột 'Tính' = 0 tính bằng 0)</t>
-        </is>
-      </c>
+      <c r="A63" s="3" t="n"/>
+      <c r="G63" s="39" t="n"/>
+      <c r="H63" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4006,7 +3751,7 @@
       </c>
       <c r="C5" s="40">
         <f>TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>

--- a/docs/travel/tour-china-2026-10-budget.xlsx
+++ b/docs/travel/tour-china-2026-10-budget.xlsx
@@ -738,7 +738,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -1896,19 +1896,19 @@
       </c>
       <c r="C6" s="18">
         <f>ChiPhi_QC!$D$23</f>
-        <v>31739325</v>
+        <v>33996925</v>
       </c>
       <c r="D6" s="18">
         <f>ChiPhi_QC!$D$25</f>
-        <v>34913257.5</v>
+        <v>37396617.5</v>
       </c>
       <c r="E6" s="18">
         <f>ChiPhi_QC!$E$23</f>
-        <v>63478650</v>
+        <v>67993850</v>
       </c>
       <c r="F6" s="18">
         <f>ChiPhi_QC!$E$25</f>
-        <v>69826515</v>
+        <v>74793235</v>
       </c>
     </row>
     <row r="7">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="F7" s="20">
         <f>SUM(F4:F6)</f>
-        <v>309562605</v>
+        <v>314529325</v>
       </c>
     </row>
     <row r="9">
@@ -3653,7 +3653,6 @@
       <c r="G61" s="36" t="n"/>
       <c r="H61" s="5" t="n"/>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="3" t="n"/>
       <c r="G63" s="39" t="n"/>
@@ -5193,7 +5192,7 @@
       </c>
       <c r="B4" s="17">
         <f>ThamSo!$D$11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5236,7 +5235,7 @@
       </c>
       <c r="B7" s="41">
         <f>$B$4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="29">
         <f>ThamSo!$B$59*ThamSo!$B$5+ThamSo!$B$60</f>
@@ -5244,11 +5243,11 @@
       </c>
       <c r="D7" s="29">
         <f>B7*C7</f>
-        <v>0</v>
+        <v>2257600</v>
       </c>
       <c r="E7" s="29">
         <f>D7*$B$2</f>
-        <v>0</v>
+        <v>4515200</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -5680,7 +5679,7 @@
       </c>
       <c r="E23" s="31">
         <f>SUM(E7:E22)</f>
-        <v>63478650</v>
+        <v>67993850</v>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
@@ -5696,11 +5695,11 @@
       </c>
       <c r="D24" s="29">
         <f>D23*ThamSo!$B$6</f>
-        <v>3173932.5</v>
+        <v>3399692.5</v>
       </c>
       <c r="E24" s="29">
         <f>E23*ThamSo!$B$6</f>
-        <v>6347865</v>
+        <v>6799385</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
@@ -5716,11 +5715,11 @@
       </c>
       <c r="D25" s="20">
         <f>D23+D24</f>
-        <v>34913257.5</v>
+        <v>37396617.5</v>
       </c>
       <c r="E25" s="20">
         <f>E23+E24</f>
-        <v>69826515</v>
+        <v>74793235</v>
       </c>
     </row>
   </sheetData>

--- a/docs/travel/tour-china-2026-10-budget.xlsx
+++ b/docs/travel/tour-china-2026-10-budget.xlsx
@@ -995,21 +995,21 @@
         </is>
       </c>
       <c r="B26" s="33" t="n">
-        <v>152</v>
+        <v>3094000</v>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>XiamenAir PKX 15:10 → HAN 17:55 (bay thẳng ban NGÀY; đêm 03→04/11 KHÔNG có VietJet thẳng)</t>
+          <t>Air China PEK 00:10 → HAN 03:15 (bay thẳng ĐÊM, từ Bắc Kinh Thủ Đô PEK)</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Trip.com+Google 22/09: nonstop chỉ Xiamen ban ngày $152; VERIFY app Vietjet lúc book</t>
+          <t>Ảnh Sếp 23/09: 3.105.000đ; rẻ hơn Xiamen + bay đêm, giữ ngày cuối</t>
         </is>
       </c>
     </row>
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="B27" s="33" t="n">
-        <v>148</v>
+        <v>3753000</v>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Trip.com 22/09: VJ3949 $148 (exclusive fare); đặt thẳng Vietjet.com có thể ~$110</t>
+          <t>Ảnh Sếp 23/09: VJ3949 4.126.000đ (từ PKX Đại Hưng)</t>
         </is>
       </c>
     </row>
@@ -1091,11 +1091,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Tàu Hangzhou East → Beijing South hạng 2</t>
+          <t>Bay Hàng Châu → Bắc Kinh (~2h15)</t>
         </is>
       </c>
       <c r="B30" s="33" t="n">
-        <v>650</v>
+        <v>520</v>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Tàu G ~4,5–5h, mở bán 15 ngày trước</t>
+          <t>Bay HGH → Bắc Kinh (China Eastern ~2h15), THAY tàu; + transfer sân bay ~1h</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>travelchinaguide 2026: 605–749 CNY</t>
+          <t>Trip.com 23/09: bay thẳng 480–560 CNY, rẻ &amp; nhanh hơn tàu 650</t>
         </is>
       </c>
     </row>
@@ -1842,19 +1842,19 @@
       </c>
       <c r="C4" s="18">
         <f>ChiPhi_HN!$D$23</f>
-        <v>37738990</v>
+        <v>36335570</v>
       </c>
       <c r="D4" s="18">
         <f>ChiPhi_HN!$D$25</f>
-        <v>41512889</v>
+        <v>39969127</v>
       </c>
       <c r="E4" s="18">
         <f>ChiPhi_HN!$E$23</f>
-        <v>75477980</v>
+        <v>72671140</v>
       </c>
       <c r="F4" s="18">
         <f>ChiPhi_HN!$E$25</f>
-        <v>83025778</v>
+        <v>79938254</v>
       </c>
     </row>
     <row r="5">
@@ -1869,19 +1869,19 @@
       </c>
       <c r="C5" s="18">
         <f>ChiPhi_SGN!$D$23</f>
-        <v>35615980</v>
+        <v>34976400</v>
       </c>
       <c r="D5" s="18">
         <f>ChiPhi_SGN!$D$25</f>
-        <v>39177578</v>
+        <v>38474040</v>
       </c>
       <c r="E5" s="18">
         <f>ChiPhi_SGN!$E$23</f>
-        <v>142463920</v>
+        <v>139905600</v>
       </c>
       <c r="F5" s="18">
         <f>ChiPhi_SGN!$E$25</f>
-        <v>156710312</v>
+        <v>153896160</v>
       </c>
     </row>
     <row r="6">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="C6" s="18">
         <f>ChiPhi_QC!$D$23</f>
-        <v>33996925</v>
+        <v>33357345</v>
       </c>
       <c r="D6" s="18">
         <f>ChiPhi_QC!$D$25</f>
-        <v>37396617.5</v>
+        <v>36693079.5</v>
       </c>
       <c r="E6" s="18">
         <f>ChiPhi_QC!$E$23</f>
-        <v>67993850</v>
+        <v>66714690</v>
       </c>
       <c r="F6" s="18">
         <f>ChiPhi_QC!$E$25</f>
-        <v>74793235</v>
+        <v>73386159</v>
       </c>
     </row>
     <row r="7">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="F7" s="20">
         <f>SUM(F4:F6)</f>
-        <v>314529325</v>
+        <v>307220573</v>
       </c>
     </row>
     <row r="9">
@@ -4115,15 +4115,15 @@
       </c>
       <c r="C9" s="29">
         <f>IF(ThamSo!$C$26="CNY",ThamSo!$B$26*ThamSo!$B$4,IF(ThamSo!$C$26="USD",ThamSo!$B$26*ThamSo!$B$5,ThamSo!$B$26))</f>
-        <v>3983920</v>
+        <v>3094000</v>
       </c>
       <c r="D9" s="29">
         <f>B9*C9</f>
-        <v>3983920</v>
+        <v>3094000</v>
       </c>
       <c r="E9" s="29">
         <f>D9*$B$2</f>
-        <v>7967840</v>
+        <v>6188000</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -4196,15 +4196,15 @@
       </c>
       <c r="C12" s="29">
         <f>IF(ThamSo!$C$30="CNY",ThamSo!$B$30*ThamSo!$B$4,IF(ThamSo!$C$30="USD",ThamSo!$B$30*ThamSo!$B$5,ThamSo!$B$30))</f>
-        <v>2567500</v>
+        <v>2054000</v>
       </c>
       <c r="D12" s="29">
         <f>B12*C12</f>
-        <v>2567500</v>
+        <v>2054000</v>
       </c>
       <c r="E12" s="29">
         <f>D12*$B$2</f>
-        <v>5135000</v>
+        <v>4108000</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E23" s="31">
         <f>SUM(E7:E22)</f>
-        <v>75477980</v>
+        <v>72671140</v>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
@@ -4517,11 +4517,11 @@
       </c>
       <c r="D24" s="29">
         <f>D23*ThamSo!$B$6</f>
-        <v>3773899</v>
+        <v>3633557</v>
       </c>
       <c r="E24" s="29">
         <f>E23*ThamSo!$B$6</f>
-        <v>7547798</v>
+        <v>7267114</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
@@ -4537,11 +4537,11 @@
       </c>
       <c r="D25" s="20">
         <f>D23+D24</f>
-        <v>41512889</v>
+        <v>39969127</v>
       </c>
       <c r="E25" s="20">
         <f>E23+E24</f>
-        <v>83025778</v>
+        <v>79938254</v>
       </c>
     </row>
   </sheetData>
@@ -4704,15 +4704,15 @@
       </c>
       <c r="C9" s="29">
         <f>IF(ThamSo!$C$27="CNY",ThamSo!$B$27*ThamSo!$B$4,IF(ThamSo!$C$27="USD",ThamSo!$B$27*ThamSo!$B$5,ThamSo!$B$27))</f>
-        <v>3879080</v>
+        <v>3753000</v>
       </c>
       <c r="D9" s="29">
         <f>B9*C9</f>
-        <v>3879080</v>
+        <v>3753000</v>
       </c>
       <c r="E9" s="29">
         <f>D9*$B$2</f>
-        <v>15516320</v>
+        <v>15012000</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -4785,15 +4785,15 @@
       </c>
       <c r="C12" s="29">
         <f>IF(ThamSo!$C$30="CNY",ThamSo!$B$30*ThamSo!$B$4,IF(ThamSo!$C$30="USD",ThamSo!$B$30*ThamSo!$B$5,ThamSo!$B$30))</f>
-        <v>2567500</v>
+        <v>2054000</v>
       </c>
       <c r="D12" s="29">
         <f>B12*C12</f>
-        <v>2567500</v>
+        <v>2054000</v>
       </c>
       <c r="E12" s="29">
         <f>D12*$B$2</f>
-        <v>10270000</v>
+        <v>8216000</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="E23" s="31">
         <f>SUM(E7:E22)</f>
-        <v>142463920</v>
+        <v>139905600</v>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
@@ -5106,11 +5106,11 @@
       </c>
       <c r="D24" s="29">
         <f>D23*ThamSo!$B$6</f>
-        <v>3561598</v>
+        <v>3497640</v>
       </c>
       <c r="E24" s="29">
         <f>E23*ThamSo!$B$6</f>
-        <v>14246392</v>
+        <v>13990560</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
@@ -5126,11 +5126,11 @@
       </c>
       <c r="D25" s="20">
         <f>D23+D24</f>
-        <v>39177578</v>
+        <v>38474040</v>
       </c>
       <c r="E25" s="20">
         <f>E23+E24</f>
-        <v>156710312</v>
+        <v>153896160</v>
       </c>
     </row>
   </sheetData>
@@ -5293,15 +5293,15 @@
       </c>
       <c r="C9" s="29">
         <f>IF(ThamSo!$C$27="CNY",ThamSo!$B$27*ThamSo!$B$4,IF(ThamSo!$C$27="USD",ThamSo!$B$27*ThamSo!$B$5,ThamSo!$B$27))</f>
-        <v>3879080</v>
+        <v>3753000</v>
       </c>
       <c r="D9" s="29">
         <f>B9*C9</f>
-        <v>3879080</v>
+        <v>3753000</v>
       </c>
       <c r="E9" s="29">
         <f>D9*$B$2</f>
-        <v>7758160</v>
+        <v>7506000</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -5374,15 +5374,15 @@
       </c>
       <c r="C12" s="29">
         <f>IF(ThamSo!$C$30="CNY",ThamSo!$B$30*ThamSo!$B$4,IF(ThamSo!$C$30="USD",ThamSo!$B$30*ThamSo!$B$5,ThamSo!$B$30))</f>
-        <v>2567500</v>
+        <v>2054000</v>
       </c>
       <c r="D12" s="29">
         <f>B12*C12</f>
-        <v>2567500</v>
+        <v>2054000</v>
       </c>
       <c r="E12" s="29">
         <f>D12*$B$2</f>
-        <v>5135000</v>
+        <v>4108000</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="E23" s="31">
         <f>SUM(E7:E22)</f>
-        <v>67993850</v>
+        <v>66714690</v>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
@@ -5695,11 +5695,11 @@
       </c>
       <c r="D24" s="29">
         <f>D23*ThamSo!$B$6</f>
-        <v>3399692.5</v>
+        <v>3335734.5</v>
       </c>
       <c r="E24" s="29">
         <f>E23*ThamSo!$B$6</f>
-        <v>6799385</v>
+        <v>6671469</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
@@ -5715,11 +5715,11 @@
       </c>
       <c r="D25" s="20">
         <f>D23+D24</f>
-        <v>37396617.5</v>
+        <v>36693079.5</v>
       </c>
       <c r="E25" s="20">
         <f>E23+E24</f>
-        <v>74793235</v>
+        <v>73386159</v>
       </c>
     </row>
   </sheetData>
